--- a/AHR 27th/AHR_data 27th dashboard.xlsx
+++ b/AHR 27th/AHR_data 27th dashboard.xlsx
@@ -10,6 +10,7 @@
     <sheet name="Individual Scores &amp; Rankings" sheetId="1" r:id="rId1"/>
     <sheet name="State Mileage" sheetId="2" r:id="rId2"/>
     <sheet name="All Rankings" sheetId="3" r:id="rId3"/>
+    <sheet name="AHR Data Full" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -21620,4 +21621,6692 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AO52"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>state</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>SHA_miles</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>state_tot_lane_miles</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>SHA_ratio</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>pct_urban_lane_miles</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>urban_lm_index</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>capital_disbursement</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>maintenance_disbursement</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>admin_disbursement</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>other_disbursement</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>rural_interstate_above_170</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>rural_interstate_total</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>rural_OPA_above_220</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>rural_OPA_total</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>urban_interstate_above_170</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>urban_interstate_total</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>urban_OPA_above_220</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>urban_OPA_total</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>rural_fatality_interstate_OFE_OPA</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>urban_fatality_interstate_OFE_OPA</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>other_fatality</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>rural_VMT_interstate_OFE_OPA</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>urban_VMT_interstate_OFE_OPA</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>other_VMT</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>total_bridges</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>total_poor_bridges</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>state_tot_commuters</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>state_tot_congestion_hours</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>capital_disbursement_perlm</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>maintenance_disbursement_perlm</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>admin_disbursement_perlm</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>other_disbursement_perlm</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>rural_interstate_poor_percent</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>urban_interstate_poor_percent</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>rural_OPA_poor_percent</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>urban_OPA_poor_percent</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>state_avg_congestion_hours</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>poor_bridges_percent</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>rural_fatalities_per_100m_VMT</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>urban_fatalities_per_100m_VMT</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>other_fatalities_per_100m_VMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Alabama</t>
+        </is>
+      </c>
+      <c r="B2">
+        <v>10941.116</v>
+      </c>
+      <c r="C2">
+        <v>29706.921</v>
+      </c>
+      <c r="D2">
+        <v>2.715163699937009</v>
+      </c>
+      <c r="E2">
+        <v>0.3145208148633108</v>
+      </c>
+      <c r="F2">
+        <v>1.123162968615401</v>
+      </c>
+      <c r="G2">
+        <v>1387759000</v>
+      </c>
+      <c r="H2">
+        <v>204894000</v>
+      </c>
+      <c r="I2">
+        <v>336541000</v>
+      </c>
+      <c r="J2">
+        <v>262696000</v>
+      </c>
+      <c r="K2">
+        <v>8.481</v>
+      </c>
+      <c r="L2">
+        <v>570.561</v>
+      </c>
+      <c r="M2">
+        <v>7.132</v>
+      </c>
+      <c r="N2">
+        <v>2046.675</v>
+      </c>
+      <c r="O2">
+        <v>22.342</v>
+      </c>
+      <c r="P2">
+        <v>432.651</v>
+      </c>
+      <c r="Q2">
+        <v>24.891</v>
+      </c>
+      <c r="R2">
+        <v>1284.213</v>
+      </c>
+      <c r="S2">
+        <v>168</v>
+      </c>
+      <c r="T2">
+        <v>220</v>
+      </c>
+      <c r="U2">
+        <v>545</v>
+      </c>
+      <c r="V2">
+        <v>11594.92568</v>
+      </c>
+      <c r="W2">
+        <v>18139.5859</v>
+      </c>
+      <c r="X2">
+        <v>38186.98526</v>
+      </c>
+      <c r="Y2">
+        <v>16164</v>
+      </c>
+      <c r="Z2">
+        <v>586</v>
+      </c>
+      <c r="AA2">
+        <v>1399570.009469596</v>
+      </c>
+      <c r="AB2">
+        <v>22727163.26257395</v>
+      </c>
+      <c r="AC2">
+        <v>46715.00624383119</v>
+      </c>
+      <c r="AD2">
+        <v>6897.180626696385</v>
+      </c>
+      <c r="AE2">
+        <v>11328.7068693521</v>
+      </c>
+      <c r="AF2">
+        <v>8842.922496074232</v>
+      </c>
+      <c r="AG2">
+        <v>1.486431775042458</v>
+      </c>
+      <c r="AH2">
+        <v>5.163977432156635</v>
+      </c>
+      <c r="AI2">
+        <v>0.3484676365324245</v>
+      </c>
+      <c r="AJ2">
+        <v>1.938229873081802</v>
+      </c>
+      <c r="AK2">
+        <v>16.23867552805523</v>
+      </c>
+      <c r="AL2">
+        <v>3.625340262311309</v>
+      </c>
+      <c r="AM2">
+        <v>1.448909675115744</v>
+      </c>
+      <c r="AN2">
+        <v>1.212817101850159</v>
+      </c>
+      <c r="AO2">
+        <v>1.427187813568711</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Alaska</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>5636.721</v>
+      </c>
+      <c r="C3">
+        <v>11754.095</v>
+      </c>
+      <c r="D3">
+        <v>2.08527173865799</v>
+      </c>
+      <c r="E3">
+        <v>0.1514196541715887</v>
+      </c>
+      <c r="F3">
+        <v>0.5407239847066722</v>
+      </c>
+      <c r="G3">
+        <v>767574000</v>
+      </c>
+      <c r="H3">
+        <v>265310000</v>
+      </c>
+      <c r="I3">
+        <v>45613000</v>
+      </c>
+      <c r="J3">
+        <v>80239000</v>
+      </c>
+      <c r="K3">
+        <v>94.49600000000001</v>
+      </c>
+      <c r="L3">
+        <v>981.503</v>
+      </c>
+      <c r="M3">
+        <v>65.82599999999999</v>
+      </c>
+      <c r="N3">
+        <v>477.814</v>
+      </c>
+      <c r="O3">
+        <v>1.326</v>
+      </c>
+      <c r="P3">
+        <v>78.42499999999998</v>
+      </c>
+      <c r="Q3">
+        <v>6.244</v>
+      </c>
+      <c r="R3">
+        <v>139.411</v>
+      </c>
+      <c r="S3">
+        <v>17</v>
+      </c>
+      <c r="T3">
+        <v>19</v>
+      </c>
+      <c r="U3">
+        <v>28</v>
+      </c>
+      <c r="V3">
+        <v>992.2211600000001</v>
+      </c>
+      <c r="W3">
+        <v>1498.34451</v>
+      </c>
+      <c r="X3">
+        <v>2815.32286</v>
+      </c>
+      <c r="Y3">
+        <v>1632</v>
+      </c>
+      <c r="Z3">
+        <v>134</v>
+      </c>
+      <c r="AA3">
+        <v>177000</v>
+      </c>
+      <c r="AB3">
+        <v>3030000</v>
+      </c>
+      <c r="AC3">
+        <v>65302.68812698893</v>
+      </c>
+      <c r="AD3">
+        <v>22571.70798772683</v>
+      </c>
+      <c r="AE3">
+        <v>3880.605014677863</v>
+      </c>
+      <c r="AF3">
+        <v>6826.471965727689</v>
+      </c>
+      <c r="AG3">
+        <v>9.627683257208588</v>
+      </c>
+      <c r="AH3">
+        <v>1.690787376474339</v>
+      </c>
+      <c r="AI3">
+        <v>13.77649043351597</v>
+      </c>
+      <c r="AJ3">
+        <v>4.478843132894821</v>
+      </c>
+      <c r="AK3">
+        <v>17.11864406779661</v>
+      </c>
+      <c r="AL3">
+        <v>8.21078431372549</v>
+      </c>
+      <c r="AM3">
+        <v>1.713327702061907</v>
+      </c>
+      <c r="AN3">
+        <v>1.268066180587534</v>
+      </c>
+      <c r="AO3">
+        <v>0.9945573347136463</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Arizona</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>6843.514</v>
+      </c>
+      <c r="C4">
+        <v>20046.092</v>
+      </c>
+      <c r="D4">
+        <v>2.929210344276347</v>
+      </c>
+      <c r="E4">
+        <v>0.2931135904195192</v>
+      </c>
+      <c r="F4">
+        <v>1.046717148116829</v>
+      </c>
+      <c r="G4">
+        <v>1375627000</v>
+      </c>
+      <c r="H4">
+        <v>161453000</v>
+      </c>
+      <c r="I4">
+        <v>224330000</v>
+      </c>
+      <c r="J4">
+        <v>395689000</v>
+      </c>
+      <c r="K4">
+        <v>20.2</v>
+      </c>
+      <c r="L4">
+        <v>909.145</v>
+      </c>
+      <c r="M4">
+        <v>13.693</v>
+      </c>
+      <c r="N4">
+        <v>1241.206</v>
+      </c>
+      <c r="O4">
+        <v>5.199999999999999</v>
+      </c>
+      <c r="P4">
+        <v>244.666</v>
+      </c>
+      <c r="Q4">
+        <v>41.608</v>
+      </c>
+      <c r="R4">
+        <v>663.92</v>
+      </c>
+      <c r="S4">
+        <v>167</v>
+      </c>
+      <c r="T4">
+        <v>331</v>
+      </c>
+      <c r="U4">
+        <v>445</v>
+      </c>
+      <c r="V4">
+        <v>10333.3868</v>
+      </c>
+      <c r="W4">
+        <v>22157.40152</v>
+      </c>
+      <c r="X4">
+        <v>33267.4908</v>
+      </c>
+      <c r="Y4">
+        <v>8467</v>
+      </c>
+      <c r="Z4">
+        <v>117</v>
+      </c>
+      <c r="AA4">
+        <v>2972000</v>
+      </c>
+      <c r="AB4">
+        <v>65840000</v>
+      </c>
+      <c r="AC4">
+        <v>68623.20097104214</v>
+      </c>
+      <c r="AD4">
+        <v>8054.088547533354</v>
+      </c>
+      <c r="AE4">
+        <v>11190.70988998753</v>
+      </c>
+      <c r="AF4">
+        <v>19738.95959372031</v>
+      </c>
+      <c r="AG4">
+        <v>2.221867798865968</v>
+      </c>
+      <c r="AH4">
+        <v>2.12534639058962</v>
+      </c>
+      <c r="AI4">
+        <v>1.103201241373309</v>
+      </c>
+      <c r="AJ4">
+        <v>6.267020122906374</v>
+      </c>
+      <c r="AK4">
+        <v>22.15343203230148</v>
+      </c>
+      <c r="AL4">
+        <v>1.381835360812566</v>
+      </c>
+      <c r="AM4">
+        <v>1.61612067013692</v>
+      </c>
+      <c r="AN4">
+        <v>1.49385748008957</v>
+      </c>
+      <c r="AO4">
+        <v>1.337642212559055</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Arkansas</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>16453.966</v>
+      </c>
+      <c r="C5">
+        <v>38078.351</v>
+      </c>
+      <c r="D5">
+        <v>2.314235425064085</v>
+      </c>
+      <c r="E5">
+        <v>0.1867015459781859</v>
+      </c>
+      <c r="F5">
+        <v>0.6667166455011155</v>
+      </c>
+      <c r="G5">
+        <v>919783000</v>
+      </c>
+      <c r="H5">
+        <v>207470000</v>
+      </c>
+      <c r="I5">
+        <v>39207000</v>
+      </c>
+      <c r="J5">
+        <v>180207000</v>
+      </c>
+      <c r="K5">
+        <v>11.64</v>
+      </c>
+      <c r="L5">
+        <v>438.905</v>
+      </c>
+      <c r="M5">
+        <v>33.661</v>
+      </c>
+      <c r="N5">
+        <v>1876.896</v>
+      </c>
+      <c r="O5">
+        <v>15.915</v>
+      </c>
+      <c r="P5">
+        <v>310.207</v>
+      </c>
+      <c r="Q5">
+        <v>61.157</v>
+      </c>
+      <c r="R5">
+        <v>617.582</v>
+      </c>
+      <c r="S5">
+        <v>77</v>
+      </c>
+      <c r="T5">
+        <v>55</v>
+      </c>
+      <c r="U5">
+        <v>189</v>
+      </c>
+      <c r="V5">
+        <v>7446.95818</v>
+      </c>
+      <c r="W5">
+        <v>9458.13616</v>
+      </c>
+      <c r="X5">
+        <v>17013.6676</v>
+      </c>
+      <c r="Y5">
+        <v>12941</v>
+      </c>
+      <c r="Z5">
+        <v>679</v>
+      </c>
+      <c r="AA5">
+        <v>715181.1414311588</v>
+      </c>
+      <c r="AB5">
+        <v>14555948.87500856</v>
+      </c>
+      <c r="AC5">
+        <v>24155.01133439313</v>
+      </c>
+      <c r="AD5">
+        <v>5448.502746350544</v>
+      </c>
+      <c r="AE5">
+        <v>1029.640175332172</v>
+      </c>
+      <c r="AF5">
+        <v>4732.531616193149</v>
+      </c>
+      <c r="AG5">
+        <v>2.652054544833164</v>
+      </c>
+      <c r="AH5">
+        <v>5.130445154364667</v>
+      </c>
+      <c r="AI5">
+        <v>1.793439807000495</v>
+      </c>
+      <c r="AJ5">
+        <v>9.902652603217062</v>
+      </c>
+      <c r="AK5">
+        <v>20.35281417779062</v>
+      </c>
+      <c r="AL5">
+        <v>5.246889730314504</v>
+      </c>
+      <c r="AM5">
+        <v>1.033979218612988</v>
+      </c>
+      <c r="AN5">
+        <v>0.5815099198148993</v>
+      </c>
+      <c r="AO5">
+        <v>1.110871591261134</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>California</t>
+        </is>
+      </c>
+      <c r="B6">
+        <v>15022.272</v>
+      </c>
+      <c r="C6">
+        <v>52003.894</v>
+      </c>
+      <c r="D6">
+        <v>3.461786206507245</v>
+      </c>
+      <c r="E6">
+        <v>0.4762250688381143</v>
+      </c>
+      <c r="F6">
+        <v>1.700613558049395</v>
+      </c>
+      <c r="G6">
+        <v>4513968000</v>
+      </c>
+      <c r="H6">
+        <v>2331366000</v>
+      </c>
+      <c r="I6">
+        <v>580307000</v>
+      </c>
+      <c r="J6">
+        <v>3364186000</v>
+      </c>
+      <c r="K6">
+        <v>54.642</v>
+      </c>
+      <c r="L6">
+        <v>1209.1</v>
+      </c>
+      <c r="M6">
+        <v>77.248</v>
+      </c>
+      <c r="N6">
+        <v>3332.69</v>
+      </c>
+      <c r="O6">
+        <v>116.589</v>
+      </c>
+      <c r="P6">
+        <v>1243.151</v>
+      </c>
+      <c r="Q6">
+        <v>2434.307</v>
+      </c>
+      <c r="R6">
+        <v>6116.816</v>
+      </c>
+      <c r="S6">
+        <v>495</v>
+      </c>
+      <c r="T6">
+        <v>1636</v>
+      </c>
+      <c r="U6">
+        <v>1710</v>
+      </c>
+      <c r="V6">
+        <v>32598.78485</v>
+      </c>
+      <c r="W6">
+        <v>170617.0324</v>
+      </c>
+      <c r="X6">
+        <v>96595.86581000002</v>
+      </c>
+      <c r="Y6">
+        <v>25737</v>
+      </c>
+      <c r="Z6">
+        <v>1493</v>
+      </c>
+      <c r="AA6">
+        <v>17330000</v>
+      </c>
+      <c r="AB6">
+        <v>543237000</v>
+      </c>
+      <c r="AC6">
+        <v>86800.57689526097</v>
+      </c>
+      <c r="AD6">
+        <v>44830.6044158924</v>
+      </c>
+      <c r="AE6">
+        <v>11158.91436898937</v>
+      </c>
+      <c r="AF6">
+        <v>64691.04025171653</v>
+      </c>
+      <c r="AG6">
+        <v>4.51922917872798</v>
+      </c>
+      <c r="AH6">
+        <v>9.378506713987278</v>
+      </c>
+      <c r="AI6">
+        <v>2.317887352258986</v>
+      </c>
+      <c r="AJ6">
+        <v>39.79696299512688</v>
+      </c>
+      <c r="AK6">
+        <v>31.3466243508367</v>
+      </c>
+      <c r="AL6">
+        <v>5.800986906010801</v>
+      </c>
+      <c r="AM6">
+        <v>1.51846150792949</v>
+      </c>
+      <c r="AN6">
+        <v>0.9588726148773409</v>
+      </c>
+      <c r="AO6">
+        <v>1.77026209730704</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Colorado</t>
+        </is>
+      </c>
+      <c r="B7">
+        <v>9031.538</v>
+      </c>
+      <c r="C7">
+        <v>23022.464</v>
+      </c>
+      <c r="D7">
+        <v>2.549118876541293</v>
+      </c>
+      <c r="E7">
+        <v>0.254561761938253</v>
+      </c>
+      <c r="F7">
+        <v>0.9090474484456369</v>
+      </c>
+      <c r="G7">
+        <v>1051281000</v>
+      </c>
+      <c r="H7">
+        <v>534394000</v>
+      </c>
+      <c r="I7">
+        <v>222838000</v>
+      </c>
+      <c r="J7">
+        <v>133271000</v>
+      </c>
+      <c r="K7">
+        <v>53.929</v>
+      </c>
+      <c r="L7">
+        <v>648.121</v>
+      </c>
+      <c r="M7">
+        <v>27.004</v>
+      </c>
+      <c r="N7">
+        <v>2568.867</v>
+      </c>
+      <c r="O7">
+        <v>20.171</v>
+      </c>
+      <c r="P7">
+        <v>303.718</v>
+      </c>
+      <c r="Q7">
+        <v>121.302</v>
+      </c>
+      <c r="R7">
+        <v>1067.407</v>
+      </c>
+      <c r="S7">
+        <v>117</v>
+      </c>
+      <c r="T7">
+        <v>258</v>
+      </c>
+      <c r="U7">
+        <v>246</v>
+      </c>
+      <c r="V7">
+        <v>9071.350409999999</v>
+      </c>
+      <c r="W7">
+        <v>21772.41377</v>
+      </c>
+      <c r="X7">
+        <v>17798.28242</v>
+      </c>
+      <c r="Y7">
+        <v>8869</v>
+      </c>
+      <c r="Z7">
+        <v>469</v>
+      </c>
+      <c r="AA7">
+        <v>2250000</v>
+      </c>
+      <c r="AB7">
+        <v>51265000</v>
+      </c>
+      <c r="AC7">
+        <v>45663.27044750727</v>
+      </c>
+      <c r="AD7">
+        <v>23211.8508253504</v>
+      </c>
+      <c r="AE7">
+        <v>9679.155106942506</v>
+      </c>
+      <c r="AF7">
+        <v>5788.737469629663</v>
+      </c>
+      <c r="AG7">
+        <v>8.320822809321099</v>
+      </c>
+      <c r="AH7">
+        <v>6.641358101923495</v>
+      </c>
+      <c r="AI7">
+        <v>1.05120272867377</v>
+      </c>
+      <c r="AJ7">
+        <v>11.3641750522528</v>
+      </c>
+      <c r="AK7">
+        <v>22.78444444444444</v>
+      </c>
+      <c r="AL7">
+        <v>5.288082083662194</v>
+      </c>
+      <c r="AM7">
+        <v>1.289774892512393</v>
+      </c>
+      <c r="AN7">
+        <v>1.184985747218784</v>
+      </c>
+      <c r="AO7">
+        <v>1.382155840630829</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Connecticut</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>3715.2</v>
+      </c>
+      <c r="C8">
+        <v>9827.219999999999</v>
+      </c>
+      <c r="D8">
+        <v>2.645138888888889</v>
+      </c>
+      <c r="E8">
+        <v>0.7440293389178222</v>
+      </c>
+      <c r="F8">
+        <v>2.656950387843398</v>
+      </c>
+      <c r="G8">
+        <v>928035000</v>
+      </c>
+      <c r="H8">
+        <v>266426000</v>
+      </c>
+      <c r="I8">
+        <v>79535000</v>
+      </c>
+      <c r="J8">
+        <v>749247000</v>
+      </c>
+      <c r="K8">
+        <v>0.21</v>
+      </c>
+      <c r="L8">
+        <v>28.74</v>
+      </c>
+      <c r="M8">
+        <v>0.96</v>
+      </c>
+      <c r="N8">
+        <v>121.97</v>
+      </c>
+      <c r="O8">
+        <v>5</v>
+      </c>
+      <c r="P8">
+        <v>317.6</v>
+      </c>
+      <c r="Q8">
+        <v>69.97</v>
+      </c>
+      <c r="R8">
+        <v>698</v>
+      </c>
+      <c r="S8">
+        <v>14</v>
+      </c>
+      <c r="T8">
+        <v>127</v>
+      </c>
+      <c r="U8">
+        <v>153</v>
+      </c>
+      <c r="V8">
+        <v>1176.44625</v>
+      </c>
+      <c r="W8">
+        <v>17102.75781</v>
+      </c>
+      <c r="X8">
+        <v>11565.7342</v>
+      </c>
+      <c r="Y8">
+        <v>4361</v>
+      </c>
+      <c r="Z8">
+        <v>231</v>
+      </c>
+      <c r="AA8">
+        <v>1624346.03925248</v>
+      </c>
+      <c r="AB8">
+        <v>49052169.52770463</v>
+      </c>
+      <c r="AC8">
+        <v>94435.15053087242</v>
+      </c>
+      <c r="AD8">
+        <v>27111.02427746606</v>
+      </c>
+      <c r="AE8">
+        <v>8093.336671001565</v>
+      </c>
+      <c r="AF8">
+        <v>76242.00943908858</v>
+      </c>
+      <c r="AG8">
+        <v>0.7306889352818373</v>
+      </c>
+      <c r="AH8">
+        <v>1.574307304785894</v>
+      </c>
+      <c r="AI8">
+        <v>0.7870787898663606</v>
+      </c>
+      <c r="AJ8">
+        <v>10.0243553008596</v>
+      </c>
+      <c r="AK8">
+        <v>30.19810332426353</v>
+      </c>
+      <c r="AL8">
+        <v>5.296950240770466</v>
+      </c>
+      <c r="AM8">
+        <v>1.190024618634298</v>
+      </c>
+      <c r="AN8">
+        <v>0.7425703001286903</v>
+      </c>
+      <c r="AO8">
+        <v>1.322873216297846</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Delaware</t>
+        </is>
+      </c>
+      <c r="B9">
+        <v>5465.57</v>
+      </c>
+      <c r="C9">
+        <v>11997.76</v>
+      </c>
+      <c r="D9">
+        <v>2.195152564142441</v>
+      </c>
+      <c r="E9">
+        <v>0.5327561144747019</v>
+      </c>
+      <c r="F9">
+        <v>1.902487564587616</v>
+      </c>
+      <c r="G9">
+        <v>591785000</v>
+      </c>
+      <c r="H9">
+        <v>450218000</v>
+      </c>
+      <c r="I9">
+        <v>357476000</v>
+      </c>
+      <c r="J9">
+        <v>380895000</v>
+      </c>
+      <c r="K9">
+        <v>0</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <v>0.61</v>
+      </c>
+      <c r="N9">
+        <v>99.25</v>
+      </c>
+      <c r="O9">
+        <v>3.5</v>
+      </c>
+      <c r="P9">
+        <v>40.38</v>
+      </c>
+      <c r="Q9">
+        <v>10.69</v>
+      </c>
+      <c r="R9">
+        <v>212.68</v>
+      </c>
+      <c r="S9">
+        <v>13</v>
+      </c>
+      <c r="T9">
+        <v>48</v>
+      </c>
+      <c r="U9">
+        <v>55</v>
+      </c>
+      <c r="V9">
+        <v>871.1909900000001</v>
+      </c>
+      <c r="W9">
+        <v>3621.6457</v>
+      </c>
+      <c r="X9">
+        <v>3852.39292</v>
+      </c>
+      <c r="Y9">
+        <v>875</v>
+      </c>
+      <c r="Z9">
+        <v>17</v>
+      </c>
+      <c r="AA9">
+        <v>344884.0573848253</v>
+      </c>
+      <c r="AB9">
+        <v>10638712.84706618</v>
+      </c>
+      <c r="AC9">
+        <v>49324.62392980023</v>
+      </c>
+      <c r="AD9">
+        <v>37525.17136532153</v>
+      </c>
+      <c r="AE9">
+        <v>29795.22844264263</v>
+      </c>
+      <c r="AF9">
+        <v>31747.17613954605</v>
+      </c>
+      <c r="AH9">
+        <v>8.667657256067359</v>
+      </c>
+      <c r="AI9">
+        <v>0.614609571788413</v>
+      </c>
+      <c r="AJ9">
+        <v>5.026330637577581</v>
+      </c>
+      <c r="AK9">
+        <v>30.84721551856306</v>
+      </c>
+      <c r="AL9">
+        <v>1.942857142857143</v>
+      </c>
+      <c r="AM9">
+        <v>1.492210106534734</v>
+      </c>
+      <c r="AN9">
+        <v>1.325364322633768</v>
+      </c>
+      <c r="AO9">
+        <v>1.427684069152531</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Florida</t>
+        </is>
+      </c>
+      <c r="B10">
+        <v>12135.832</v>
+      </c>
+      <c r="C10">
+        <v>45012.826</v>
+      </c>
+      <c r="D10">
+        <v>3.709084469857526</v>
+      </c>
+      <c r="E10">
+        <v>0.6396291137108343</v>
+      </c>
+      <c r="F10">
+        <v>2.284134150169091</v>
+      </c>
+      <c r="G10">
+        <v>6509736000</v>
+      </c>
+      <c r="H10">
+        <v>1495838000</v>
+      </c>
+      <c r="I10">
+        <v>450415000</v>
+      </c>
+      <c r="J10">
+        <v>2430777000</v>
+      </c>
+      <c r="K10">
+        <v>1.099</v>
+      </c>
+      <c r="L10">
+        <v>717.2670000000001</v>
+      </c>
+      <c r="M10">
+        <v>4.351</v>
+      </c>
+      <c r="N10">
+        <v>2596.855</v>
+      </c>
+      <c r="O10">
+        <v>12.393</v>
+      </c>
+      <c r="P10">
+        <v>777.899</v>
+      </c>
+      <c r="Q10">
+        <v>81.075</v>
+      </c>
+      <c r="R10">
+        <v>3879.958</v>
+      </c>
+      <c r="S10">
+        <v>370</v>
+      </c>
+      <c r="T10">
+        <v>1328</v>
+      </c>
+      <c r="U10">
+        <v>1308</v>
+      </c>
+      <c r="V10">
+        <v>20614.21318</v>
+      </c>
+      <c r="W10">
+        <v>85565.92676</v>
+      </c>
+      <c r="X10">
+        <v>101895.77894</v>
+      </c>
+      <c r="Y10">
+        <v>12680</v>
+      </c>
+      <c r="Z10">
+        <v>459</v>
+      </c>
+      <c r="AA10">
+        <v>9347230.621102002</v>
+      </c>
+      <c r="AB10">
+        <v>175560843.043142</v>
+      </c>
+      <c r="AC10">
+        <v>144619.5802058729</v>
+      </c>
+      <c r="AD10">
+        <v>33231.37276473155</v>
+      </c>
+      <c r="AE10">
+        <v>10006.3701843559</v>
+      </c>
+      <c r="AF10">
+        <v>54001.8749322693</v>
+      </c>
+      <c r="AG10">
+        <v>0.1532204883258257</v>
+      </c>
+      <c r="AH10">
+        <v>1.593137412440432</v>
+      </c>
+      <c r="AI10">
+        <v>0.1675488234807103</v>
+      </c>
+      <c r="AJ10">
+        <v>2.089584474883491</v>
+      </c>
+      <c r="AK10">
+        <v>18.78212383535307</v>
+      </c>
+      <c r="AL10">
+        <v>3.6198738170347</v>
+      </c>
+      <c r="AM10">
+        <v>1.794878110404794</v>
+      </c>
+      <c r="AN10">
+        <v>1.552019653482919</v>
+      </c>
+      <c r="AO10">
+        <v>1.283664557655719</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Georgia</t>
+        </is>
+      </c>
+      <c r="B11">
+        <v>17923.171</v>
+      </c>
+      <c r="C11">
+        <v>49496.955</v>
+      </c>
+      <c r="D11">
+        <v>2.761618186871062</v>
+      </c>
+      <c r="E11">
+        <v>0.3830902325203641</v>
+      </c>
+      <c r="F11">
+        <v>1.368026351426473</v>
+      </c>
+      <c r="G11">
+        <v>1564658000</v>
+      </c>
+      <c r="H11">
+        <v>616874000</v>
+      </c>
+      <c r="I11">
+        <v>484060000</v>
+      </c>
+      <c r="J11">
+        <v>641050000</v>
+      </c>
+      <c r="K11">
+        <v>4.875</v>
+      </c>
+      <c r="L11">
+        <v>538.251</v>
+      </c>
+      <c r="M11">
+        <v>9.272</v>
+      </c>
+      <c r="N11">
+        <v>2428.363</v>
+      </c>
+      <c r="O11">
+        <v>9.628</v>
+      </c>
+      <c r="P11">
+        <v>708.8099999999999</v>
+      </c>
+      <c r="Q11">
+        <v>46.455</v>
+      </c>
+      <c r="R11">
+        <v>2355.549</v>
+      </c>
+      <c r="S11">
+        <v>185</v>
+      </c>
+      <c r="T11">
+        <v>506</v>
+      </c>
+      <c r="U11">
+        <v>970</v>
+      </c>
+      <c r="V11">
+        <v>13525.43715</v>
+      </c>
+      <c r="W11">
+        <v>42303.02504</v>
+      </c>
+      <c r="X11">
+        <v>60138.36442</v>
+      </c>
+      <c r="Y11">
+        <v>14987</v>
+      </c>
+      <c r="Z11">
+        <v>319</v>
+      </c>
+      <c r="AA11">
+        <v>3543897.447326517</v>
+      </c>
+      <c r="AB11">
+        <v>102574143.9982804</v>
+      </c>
+      <c r="AC11">
+        <v>31611.19709283127</v>
+      </c>
+      <c r="AD11">
+        <v>12462.86766529375</v>
+      </c>
+      <c r="AE11">
+        <v>9779.591492042287</v>
+      </c>
+      <c r="AF11">
+        <v>12951.30175179463</v>
+      </c>
+      <c r="AG11">
+        <v>0.9057112759660457</v>
+      </c>
+      <c r="AH11">
+        <v>1.358332980629506</v>
+      </c>
+      <c r="AI11">
+        <v>0.3818210045203291</v>
+      </c>
+      <c r="AJ11">
+        <v>1.972151714950527</v>
+      </c>
+      <c r="AK11">
+        <v>28.94388043752829</v>
+      </c>
+      <c r="AL11">
+        <v>2.128511376526323</v>
+      </c>
+      <c r="AM11">
+        <v>1.367793128963673</v>
+      </c>
+      <c r="AN11">
+        <v>1.196131953971488</v>
+      </c>
+      <c r="AO11">
+        <v>1.612947091852419</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="B12">
+        <v>948.6559999999999</v>
+      </c>
+      <c r="C12">
+        <v>2477.288</v>
+      </c>
+      <c r="D12">
+        <v>2.611365974599855</v>
+      </c>
+      <c r="E12">
+        <v>0.6093058215274122</v>
+      </c>
+      <c r="F12">
+        <v>2.175848792706419</v>
+      </c>
+      <c r="G12">
+        <v>243071000</v>
+      </c>
+      <c r="H12">
+        <v>60106000</v>
+      </c>
+      <c r="I12">
+        <v>18764000</v>
+      </c>
+      <c r="J12">
+        <v>63018000</v>
+      </c>
+      <c r="K12">
+        <v>0</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12">
+        <v>3.219</v>
+      </c>
+      <c r="N12">
+        <v>77.349</v>
+      </c>
+      <c r="O12">
+        <v>14.141</v>
+      </c>
+      <c r="P12">
+        <v>54.639</v>
+      </c>
+      <c r="Q12">
+        <v>31.517</v>
+      </c>
+      <c r="R12">
+        <v>261.275</v>
+      </c>
+      <c r="S12">
+        <v>7</v>
+      </c>
+      <c r="T12">
+        <v>47</v>
+      </c>
+      <c r="U12">
+        <v>31</v>
+      </c>
+      <c r="V12">
+        <v>242.27314</v>
+      </c>
+      <c r="W12">
+        <v>3781.14601</v>
+      </c>
+      <c r="X12">
+        <v>4761.94738</v>
+      </c>
+      <c r="Y12">
+        <v>1162</v>
+      </c>
+      <c r="Z12">
+        <v>87</v>
+      </c>
+      <c r="AA12">
+        <v>485000</v>
+      </c>
+      <c r="AB12">
+        <v>10024000</v>
+      </c>
+      <c r="AC12">
+        <v>98119.79874766276</v>
+      </c>
+      <c r="AD12">
+        <v>24262.82289342216</v>
+      </c>
+      <c r="AE12">
+        <v>7574.412018303887</v>
+      </c>
+      <c r="AF12">
+        <v>25438.30188496453</v>
+      </c>
+      <c r="AH12">
+        <v>25.8807811270338</v>
+      </c>
+      <c r="AI12">
+        <v>4.161656905713066</v>
+      </c>
+      <c r="AJ12">
+        <v>12.06276911300354</v>
+      </c>
+      <c r="AK12">
+        <v>20.6680412371134</v>
+      </c>
+      <c r="AL12">
+        <v>7.487091222030981</v>
+      </c>
+      <c r="AM12">
+        <v>2.889300894023993</v>
+      </c>
+      <c r="AN12">
+        <v>1.243009391218934</v>
+      </c>
+      <c r="AO12">
+        <v>0.650994173732344</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Idaho</t>
+        </is>
+      </c>
+      <c r="B13">
+        <v>4968.194</v>
+      </c>
+      <c r="C13">
+        <v>12272.361</v>
+      </c>
+      <c r="D13">
+        <v>2.470185544284301</v>
+      </c>
+      <c r="E13">
+        <v>0.1156492218571471</v>
+      </c>
+      <c r="F13">
+        <v>0.4129867315636496</v>
+      </c>
+      <c r="G13">
+        <v>602942000</v>
+      </c>
+      <c r="H13">
+        <v>112824000</v>
+      </c>
+      <c r="I13">
+        <v>32451000</v>
+      </c>
+      <c r="J13">
+        <v>95071000</v>
+      </c>
+      <c r="K13">
+        <v>10.789</v>
+      </c>
+      <c r="L13">
+        <v>519.4450000000001</v>
+      </c>
+      <c r="M13">
+        <v>54.303</v>
+      </c>
+      <c r="N13">
+        <v>1689.282</v>
+      </c>
+      <c r="O13">
+        <v>1.527</v>
+      </c>
+      <c r="P13">
+        <v>91.768</v>
+      </c>
+      <c r="Q13">
+        <v>47.887</v>
+      </c>
+      <c r="R13">
+        <v>361.91</v>
+      </c>
+      <c r="S13">
+        <v>85</v>
+      </c>
+      <c r="T13">
+        <v>20</v>
+      </c>
+      <c r="U13">
+        <v>109</v>
+      </c>
+      <c r="V13">
+        <v>5170.93727</v>
+      </c>
+      <c r="W13">
+        <v>3895.8963</v>
+      </c>
+      <c r="X13">
+        <v>8339.584049999999</v>
+      </c>
+      <c r="Y13">
+        <v>4561</v>
+      </c>
+      <c r="Z13">
+        <v>238</v>
+      </c>
+      <c r="AA13">
+        <v>484621.8849822858</v>
+      </c>
+      <c r="AB13">
+        <v>5492487.539929143</v>
+      </c>
+      <c r="AC13">
+        <v>49130.07366716152</v>
+      </c>
+      <c r="AD13">
+        <v>9193.341036822498</v>
+      </c>
+      <c r="AE13">
+        <v>2644.234471264331</v>
+      </c>
+      <c r="AF13">
+        <v>7746.757123588525</v>
+      </c>
+      <c r="AG13">
+        <v>2.077024516551319</v>
+      </c>
+      <c r="AH13">
+        <v>1.663978728968703</v>
+      </c>
+      <c r="AI13">
+        <v>3.214560979161561</v>
+      </c>
+      <c r="AJ13">
+        <v>13.23174269846094</v>
+      </c>
+      <c r="AK13">
+        <v>11.3335524253716</v>
+      </c>
+      <c r="AL13">
+        <v>5.218153913615435</v>
+      </c>
+      <c r="AM13">
+        <v>1.643802575079391</v>
+      </c>
+      <c r="AN13">
+        <v>0.5133606867308045</v>
+      </c>
+      <c r="AO13">
+        <v>1.307019622879153</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Illinois</t>
+        </is>
+      </c>
+      <c r="B14">
+        <v>15894.14</v>
+      </c>
+      <c r="C14">
+        <v>42168.83</v>
+      </c>
+      <c r="D14">
+        <v>2.653105484159571</v>
+      </c>
+      <c r="E14">
+        <v>0.4317376128291915</v>
+      </c>
+      <c r="F14">
+        <v>1.541747560010938</v>
+      </c>
+      <c r="G14">
+        <v>3146026000</v>
+      </c>
+      <c r="H14">
+        <v>928708000</v>
+      </c>
+      <c r="I14">
+        <v>179114000</v>
+      </c>
+      <c r="J14">
+        <v>953114000</v>
+      </c>
+      <c r="K14">
+        <v>16.62</v>
+      </c>
+      <c r="L14">
+        <v>1243.34</v>
+      </c>
+      <c r="M14">
+        <v>57.83</v>
+      </c>
+      <c r="N14">
+        <v>2360.12</v>
+      </c>
+      <c r="O14">
+        <v>45.38</v>
+      </c>
+      <c r="P14">
+        <v>941.7</v>
+      </c>
+      <c r="Q14">
+        <v>331.41</v>
+      </c>
+      <c r="R14">
+        <v>2887.21</v>
+      </c>
+      <c r="S14">
+        <v>109</v>
+      </c>
+      <c r="T14">
+        <v>395</v>
+      </c>
+      <c r="U14">
+        <v>661</v>
+      </c>
+      <c r="V14">
+        <v>11863.11952</v>
+      </c>
+      <c r="W14">
+        <v>38702.49647</v>
+      </c>
+      <c r="X14">
+        <v>43554.98136999999</v>
+      </c>
+      <c r="Y14">
+        <v>26846</v>
+      </c>
+      <c r="Z14">
+        <v>2405</v>
+      </c>
+      <c r="AA14">
+        <v>4234945.524004105</v>
+      </c>
+      <c r="AB14">
+        <v>135477125.9181575</v>
+      </c>
+      <c r="AC14">
+        <v>74605.48466722932</v>
+      </c>
+      <c r="AD14">
+        <v>22023.56574749643</v>
+      </c>
+      <c r="AE14">
+        <v>4247.544928327392</v>
+      </c>
+      <c r="AF14">
+        <v>22602.33447311675</v>
+      </c>
+      <c r="AG14">
+        <v>1.336722055109624</v>
+      </c>
+      <c r="AH14">
+        <v>4.818944462142933</v>
+      </c>
+      <c r="AI14">
+        <v>2.450299137332</v>
+      </c>
+      <c r="AJ14">
+        <v>11.47855542201641</v>
+      </c>
+      <c r="AK14">
+        <v>31.99028774992718</v>
+      </c>
+      <c r="AL14">
+        <v>8.958504060195187</v>
+      </c>
+      <c r="AM14">
+        <v>0.9188139748254007</v>
+      </c>
+      <c r="AN14">
+        <v>1.020605997099391</v>
+      </c>
+      <c r="AO14">
+        <v>1.517622047372259</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Indiana</t>
+        </is>
+      </c>
+      <c r="B15">
+        <v>11029.486</v>
+      </c>
+      <c r="C15">
+        <v>28444.825</v>
+      </c>
+      <c r="D15">
+        <v>2.578980108411217</v>
+      </c>
+      <c r="E15">
+        <v>0.2772299003421536</v>
+      </c>
+      <c r="F15">
+        <v>0.9899960293329608</v>
+      </c>
+      <c r="G15">
+        <v>1554090000</v>
+      </c>
+      <c r="H15">
+        <v>919218000</v>
+      </c>
+      <c r="I15">
+        <v>106962000</v>
+      </c>
+      <c r="J15">
+        <v>126147000</v>
+      </c>
+      <c r="K15">
+        <v>21.232</v>
+      </c>
+      <c r="L15">
+        <v>768.9450000000001</v>
+      </c>
+      <c r="M15">
+        <v>7.346</v>
+      </c>
+      <c r="N15">
+        <v>1969.518</v>
+      </c>
+      <c r="O15">
+        <v>20.853</v>
+      </c>
+      <c r="P15">
+        <v>491.889</v>
+      </c>
+      <c r="Q15">
+        <v>114.338</v>
+      </c>
+      <c r="R15">
+        <v>1717.31</v>
+      </c>
+      <c r="S15">
+        <v>185</v>
+      </c>
+      <c r="T15">
+        <v>195</v>
+      </c>
+      <c r="U15">
+        <v>517</v>
+      </c>
+      <c r="V15">
+        <v>12724.29645</v>
+      </c>
+      <c r="W15">
+        <v>20302.47864</v>
+      </c>
+      <c r="X15">
+        <v>43580.9654</v>
+      </c>
+      <c r="Y15">
+        <v>19337</v>
+      </c>
+      <c r="Z15">
+        <v>1082</v>
+      </c>
+      <c r="AA15">
+        <v>2147726.054890204</v>
+      </c>
+      <c r="AB15">
+        <v>41633788.21083406</v>
+      </c>
+      <c r="AC15">
+        <v>54635.24560267114</v>
+      </c>
+      <c r="AD15">
+        <v>32315.82546210075</v>
+      </c>
+      <c r="AE15">
+        <v>3760.332503363968</v>
+      </c>
+      <c r="AF15">
+        <v>4434.796136028258</v>
+      </c>
+      <c r="AG15">
+        <v>2.761185780517462</v>
+      </c>
+      <c r="AH15">
+        <v>4.239371077621171</v>
+      </c>
+      <c r="AI15">
+        <v>0.3729846591907259</v>
+      </c>
+      <c r="AJ15">
+        <v>6.657970896343699</v>
+      </c>
+      <c r="AK15">
+        <v>19.3850552383239</v>
+      </c>
+      <c r="AL15">
+        <v>5.595490510420437</v>
+      </c>
+      <c r="AM15">
+        <v>1.453911426277718</v>
+      </c>
+      <c r="AN15">
+        <v>0.9604738586736421</v>
+      </c>
+      <c r="AO15">
+        <v>1.186297722537372</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Iowa</t>
+        </is>
+      </c>
+      <c r="B16">
+        <v>8904.574000000001</v>
+      </c>
+      <c r="C16">
+        <v>22917.695</v>
+      </c>
+      <c r="D16">
+        <v>2.573699202230225</v>
+      </c>
+      <c r="E16">
+        <v>0.1672412517925559</v>
+      </c>
+      <c r="F16">
+        <v>0.5972233695245793</v>
+      </c>
+      <c r="G16">
+        <v>1011405000</v>
+      </c>
+      <c r="H16">
+        <v>227049000</v>
+      </c>
+      <c r="I16">
+        <v>68947000</v>
+      </c>
+      <c r="J16">
+        <v>145376000</v>
+      </c>
+      <c r="K16">
+        <v>9.468999999999999</v>
+      </c>
+      <c r="L16">
+        <v>610.413</v>
+      </c>
+      <c r="M16">
+        <v>62.225</v>
+      </c>
+      <c r="N16">
+        <v>3387.07</v>
+      </c>
+      <c r="O16">
+        <v>8.375</v>
+      </c>
+      <c r="P16">
+        <v>177.535</v>
+      </c>
+      <c r="Q16">
+        <v>94.381</v>
+      </c>
+      <c r="R16">
+        <v>896.72</v>
+      </c>
+      <c r="S16">
+        <v>85</v>
+      </c>
+      <c r="T16">
+        <v>60</v>
+      </c>
+      <c r="U16">
+        <v>192</v>
+      </c>
+      <c r="V16">
+        <v>10106.30789</v>
+      </c>
+      <c r="W16">
+        <v>6305.85214</v>
+      </c>
+      <c r="X16">
+        <v>13339.33672</v>
+      </c>
+      <c r="Y16">
+        <v>23870</v>
+      </c>
+      <c r="Z16">
+        <v>4504</v>
+      </c>
+      <c r="AA16">
+        <v>757551.050227013</v>
+      </c>
+      <c r="AB16">
+        <v>5680593.51900314</v>
+      </c>
+      <c r="AC16">
+        <v>44132.05603792179</v>
+      </c>
+      <c r="AD16">
+        <v>9907.148166515</v>
+      </c>
+      <c r="AE16">
+        <v>3008.461365769987</v>
+      </c>
+      <c r="AF16">
+        <v>6343.395354550273</v>
+      </c>
+      <c r="AG16">
+        <v>1.551244812938125</v>
+      </c>
+      <c r="AH16">
+        <v>4.717379671614048</v>
+      </c>
+      <c r="AI16">
+        <v>1.837133569722503</v>
+      </c>
+      <c r="AJ16">
+        <v>10.52513605138728</v>
+      </c>
+      <c r="AK16">
+        <v>7.49862800309082</v>
+      </c>
+      <c r="AL16">
+        <v>18.86887306242145</v>
+      </c>
+      <c r="AM16">
+        <v>0.8410588805047775</v>
+      </c>
+      <c r="AN16">
+        <v>0.9514970961561431</v>
+      </c>
+      <c r="AO16">
+        <v>1.439351926037894</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Kansas</t>
+        </is>
+      </c>
+      <c r="B17">
+        <v>10296.549</v>
+      </c>
+      <c r="C17">
+        <v>24037.406</v>
+      </c>
+      <c r="D17">
+        <v>2.334510912345485</v>
+      </c>
+      <c r="E17">
+        <v>0.1246887871345186</v>
+      </c>
+      <c r="F17">
+        <v>0.4452672818233761</v>
+      </c>
+      <c r="G17">
+        <v>445765000</v>
+      </c>
+      <c r="H17">
+        <v>191848000</v>
+      </c>
+      <c r="I17">
+        <v>80775000</v>
+      </c>
+      <c r="J17">
+        <v>488543000</v>
+      </c>
+      <c r="K17">
+        <v>4.73</v>
+      </c>
+      <c r="L17">
+        <v>639.501</v>
+      </c>
+      <c r="M17">
+        <v>8.539999999999999</v>
+      </c>
+      <c r="N17">
+        <v>2628.83</v>
+      </c>
+      <c r="O17">
+        <v>7.23</v>
+      </c>
+      <c r="P17">
+        <v>234.606</v>
+      </c>
+      <c r="Q17">
+        <v>21.656</v>
+      </c>
+      <c r="R17">
+        <v>312.222</v>
+      </c>
+      <c r="S17">
+        <v>96</v>
+      </c>
+      <c r="T17">
+        <v>64</v>
+      </c>
+      <c r="U17">
+        <v>266</v>
+      </c>
+      <c r="V17">
+        <v>7546.83194</v>
+      </c>
+      <c r="W17">
+        <v>6238.48824</v>
+      </c>
+      <c r="X17">
+        <v>14068.4817</v>
+      </c>
+      <c r="Y17">
+        <v>24925</v>
+      </c>
+      <c r="Z17">
+        <v>1277</v>
+      </c>
+      <c r="AA17">
+        <v>761707.6371150416</v>
+      </c>
+      <c r="AB17">
+        <v>18792408.23745628</v>
+      </c>
+      <c r="AC17">
+        <v>18544.63830248572</v>
+      </c>
+      <c r="AD17">
+        <v>7981.227258881428</v>
+      </c>
+      <c r="AE17">
+        <v>3360.387555961737</v>
+      </c>
+      <c r="AF17">
+        <v>20324.28124731928</v>
+      </c>
+      <c r="AG17">
+        <v>0.7396391874289486</v>
+      </c>
+      <c r="AH17">
+        <v>3.081762614766886</v>
+      </c>
+      <c r="AI17">
+        <v>0.3248593480749991</v>
+      </c>
+      <c r="AJ17">
+        <v>6.936090345971777</v>
+      </c>
+      <c r="AK17">
+        <v>24.67141895627081</v>
+      </c>
+      <c r="AL17">
+        <v>5.123370110330993</v>
+      </c>
+      <c r="AM17">
+        <v>1.272056947381818</v>
+      </c>
+      <c r="AN17">
+        <v>1.025889567117305</v>
+      </c>
+      <c r="AO17">
+        <v>1.890751295500494</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Kentucky</t>
+        </is>
+      </c>
+      <c r="B18">
+        <v>27689.692</v>
+      </c>
+      <c r="C18">
+        <v>62345.847</v>
+      </c>
+      <c r="D18">
+        <v>2.251590483563342</v>
+      </c>
+      <c r="E18">
+        <v>0.1476454879183853</v>
+      </c>
+      <c r="F18">
+        <v>0.5272463273540476</v>
+      </c>
+      <c r="G18">
+        <v>1293161000</v>
+      </c>
+      <c r="H18">
+        <v>486934000</v>
+      </c>
+      <c r="I18">
+        <v>34405000</v>
+      </c>
+      <c r="J18">
+        <v>438581000</v>
+      </c>
+      <c r="K18">
+        <v>5.678</v>
+      </c>
+      <c r="L18">
+        <v>710.297</v>
+      </c>
+      <c r="M18">
+        <v>6.416</v>
+      </c>
+      <c r="N18">
+        <v>1229.06</v>
+      </c>
+      <c r="O18">
+        <v>5.332999999999999</v>
+      </c>
+      <c r="P18">
+        <v>230.024</v>
+      </c>
+      <c r="Q18">
+        <v>22.184</v>
+      </c>
+      <c r="R18">
+        <v>622.471</v>
+      </c>
+      <c r="S18">
+        <v>150</v>
+      </c>
+      <c r="T18">
+        <v>143</v>
+      </c>
+      <c r="U18">
+        <v>484</v>
+      </c>
+      <c r="V18">
+        <v>12617.92559</v>
+      </c>
+      <c r="W18">
+        <v>11330.46981</v>
+      </c>
+      <c r="X18">
+        <v>22587.41104</v>
+      </c>
+      <c r="Y18">
+        <v>14410</v>
+      </c>
+      <c r="Z18">
+        <v>990</v>
+      </c>
+      <c r="AA18">
+        <v>1110094.110957969</v>
+      </c>
+      <c r="AB18">
+        <v>21037745.92168032</v>
+      </c>
+      <c r="AC18">
+        <v>20741.73440935047</v>
+      </c>
+      <c r="AD18">
+        <v>7810.207470595435</v>
+      </c>
+      <c r="AE18">
+        <v>551.8410873462028</v>
+      </c>
+      <c r="AF18">
+        <v>7034.646590012643</v>
+      </c>
+      <c r="AG18">
+        <v>0.799383919684301</v>
+      </c>
+      <c r="AH18">
+        <v>2.318453726567662</v>
+      </c>
+      <c r="AI18">
+        <v>0.5220249621662083</v>
+      </c>
+      <c r="AJ18">
+        <v>3.563860806366883</v>
+      </c>
+      <c r="AK18">
+        <v>18.95131747300736</v>
+      </c>
+      <c r="AL18">
+        <v>6.870229007633588</v>
+      </c>
+      <c r="AM18">
+        <v>1.188784946702162</v>
+      </c>
+      <c r="AN18">
+        <v>1.262083588747499</v>
+      </c>
+      <c r="AO18">
+        <v>2.14278652450644</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Louisiana</t>
+        </is>
+      </c>
+      <c r="B19">
+        <v>17104.45</v>
+      </c>
+      <c r="C19">
+        <v>40153.939</v>
+      </c>
+      <c r="D19">
+        <v>2.347572649222863</v>
+      </c>
+      <c r="E19">
+        <v>0.280237811787282</v>
+      </c>
+      <c r="F19">
+        <v>1.000737368501597</v>
+      </c>
+      <c r="G19">
+        <v>886746000</v>
+      </c>
+      <c r="H19">
+        <v>433915000</v>
+      </c>
+      <c r="I19">
+        <v>53776000</v>
+      </c>
+      <c r="J19">
+        <v>257447000</v>
+      </c>
+      <c r="K19">
+        <v>16.144</v>
+      </c>
+      <c r="L19">
+        <v>526.579</v>
+      </c>
+      <c r="M19">
+        <v>23.449</v>
+      </c>
+      <c r="N19">
+        <v>1007.778</v>
+      </c>
+      <c r="O19">
+        <v>49.631</v>
+      </c>
+      <c r="P19">
+        <v>414.04</v>
+      </c>
+      <c r="Q19">
+        <v>151.91</v>
+      </c>
+      <c r="R19">
+        <v>956.112</v>
+      </c>
+      <c r="S19">
+        <v>99</v>
+      </c>
+      <c r="T19">
+        <v>228</v>
+      </c>
+      <c r="U19">
+        <v>497</v>
+      </c>
+      <c r="V19">
+        <v>8908.47797</v>
+      </c>
+      <c r="W19">
+        <v>15956.06196</v>
+      </c>
+      <c r="X19">
+        <v>23509.5665</v>
+      </c>
+      <c r="Y19">
+        <v>12782</v>
+      </c>
+      <c r="Z19">
+        <v>1631</v>
+      </c>
+      <c r="AA19">
+        <v>1627000</v>
+      </c>
+      <c r="AB19">
+        <v>31788000</v>
+      </c>
+      <c r="AC19">
+        <v>22083.66158049899</v>
+      </c>
+      <c r="AD19">
+        <v>10806.28727358479</v>
+      </c>
+      <c r="AE19">
+        <v>1339.245945460046</v>
+      </c>
+      <c r="AF19">
+        <v>6411.500500610911</v>
+      </c>
+      <c r="AG19">
+        <v>3.065826780027308</v>
+      </c>
+      <c r="AH19">
+        <v>11.98700608636847</v>
+      </c>
+      <c r="AI19">
+        <v>2.326802133009453</v>
+      </c>
+      <c r="AJ19">
+        <v>15.88830597252205</v>
+      </c>
+      <c r="AK19">
+        <v>19.53779963122311</v>
+      </c>
+      <c r="AL19">
+        <v>12.76013143483023</v>
+      </c>
+      <c r="AM19">
+        <v>1.111300946507252</v>
+      </c>
+      <c r="AN19">
+        <v>1.42892400751244</v>
+      </c>
+      <c r="AO19">
+        <v>2.114033025662128</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Maine</t>
+        </is>
+      </c>
+      <c r="B20">
+        <v>8340.194</v>
+      </c>
+      <c r="C20">
+        <v>17467.309</v>
+      </c>
+      <c r="D20">
+        <v>2.094352841192903</v>
+      </c>
+      <c r="E20">
+        <v>0.1345378386562006</v>
+      </c>
+      <c r="F20">
+        <v>0.4804385309820236</v>
+      </c>
+      <c r="G20">
+        <v>486290000</v>
+      </c>
+      <c r="H20">
+        <v>251308000</v>
+      </c>
+      <c r="I20">
+        <v>22799000</v>
+      </c>
+      <c r="J20">
+        <v>99599000</v>
+      </c>
+      <c r="K20">
+        <v>3.88</v>
+      </c>
+      <c r="L20">
+        <v>279.28</v>
+      </c>
+      <c r="M20">
+        <v>30.51</v>
+      </c>
+      <c r="N20">
+        <v>791.8959999999998</v>
+      </c>
+      <c r="O20">
+        <v>1.24</v>
+      </c>
+      <c r="P20">
+        <v>86.98999999999998</v>
+      </c>
+      <c r="Q20">
+        <v>13.18</v>
+      </c>
+      <c r="R20">
+        <v>120.084</v>
+      </c>
+      <c r="S20">
+        <v>28</v>
+      </c>
+      <c r="T20">
+        <v>9</v>
+      </c>
+      <c r="U20">
+        <v>126</v>
+      </c>
+      <c r="V20">
+        <v>3381.44709</v>
+      </c>
+      <c r="W20">
+        <v>1726.3128</v>
+      </c>
+      <c r="X20">
+        <v>7978.65737</v>
+      </c>
+      <c r="Y20">
+        <v>2485</v>
+      </c>
+      <c r="Z20">
+        <v>314</v>
+      </c>
+      <c r="AA20">
+        <v>197131.8351901074</v>
+      </c>
+      <c r="AB20">
+        <v>2902313.121130663</v>
+      </c>
+      <c r="AC20">
+        <v>27840.00672341687</v>
+      </c>
+      <c r="AD20">
+        <v>14387.33350397591</v>
+      </c>
+      <c r="AE20">
+        <v>1305.238259654077</v>
+      </c>
+      <c r="AF20">
+        <v>5702.023133614915</v>
+      </c>
+      <c r="AG20">
+        <v>1.389286737324549</v>
+      </c>
+      <c r="AH20">
+        <v>1.425451201287505</v>
+      </c>
+      <c r="AI20">
+        <v>3.852778647701214</v>
+      </c>
+      <c r="AJ20">
+        <v>10.97565037806869</v>
+      </c>
+      <c r="AK20">
+        <v>14.72270127415883</v>
+      </c>
+      <c r="AL20">
+        <v>12.63581488933602</v>
+      </c>
+      <c r="AM20">
+        <v>0.8280478521401321</v>
+      </c>
+      <c r="AN20">
+        <v>0.5213423662270243</v>
+      </c>
+      <c r="AO20">
+        <v>1.579213070030603</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Maryland</t>
+        </is>
+      </c>
+      <c r="B21">
+        <v>5207.452</v>
+      </c>
+      <c r="C21">
+        <v>14927.941</v>
+      </c>
+      <c r="D21">
+        <v>2.866649755004943</v>
+      </c>
+      <c r="E21">
+        <v>0.5865317929646157</v>
+      </c>
+      <c r="F21">
+        <v>2.094522074984926</v>
+      </c>
+      <c r="G21">
+        <v>1520245000</v>
+      </c>
+      <c r="H21">
+        <v>420904000</v>
+      </c>
+      <c r="I21">
+        <v>118806000</v>
+      </c>
+      <c r="J21">
+        <v>1128698000</v>
+      </c>
+      <c r="K21">
+        <v>1.76</v>
+      </c>
+      <c r="L21">
+        <v>142.136</v>
+      </c>
+      <c r="M21">
+        <v>3.245</v>
+      </c>
+      <c r="N21">
+        <v>320.815</v>
+      </c>
+      <c r="O21">
+        <v>23.311</v>
+      </c>
+      <c r="P21">
+        <v>335.891</v>
+      </c>
+      <c r="Q21">
+        <v>171.725</v>
+      </c>
+      <c r="R21">
+        <v>1021.601</v>
+      </c>
+      <c r="S21">
+        <v>23</v>
+      </c>
+      <c r="T21">
+        <v>271</v>
+      </c>
+      <c r="U21">
+        <v>271</v>
+      </c>
+      <c r="V21">
+        <v>4001.6127</v>
+      </c>
+      <c r="W21">
+        <v>27573.56035</v>
+      </c>
+      <c r="X21">
+        <v>19309.95077</v>
+      </c>
+      <c r="Y21">
+        <v>5446</v>
+      </c>
+      <c r="Z21">
+        <v>253</v>
+      </c>
+      <c r="AA21">
+        <v>1809973.049155875</v>
+      </c>
+      <c r="AB21">
+        <v>42472565.96962119</v>
+      </c>
+      <c r="AC21">
+        <v>101838.8939238171</v>
+      </c>
+      <c r="AD21">
+        <v>28195.71701147532</v>
+      </c>
+      <c r="AE21">
+        <v>7958.63274111279</v>
+      </c>
+      <c r="AF21">
+        <v>75609.75756803968</v>
+      </c>
+      <c r="AG21">
+        <v>1.238250689480498</v>
+      </c>
+      <c r="AH21">
+        <v>6.940049003992366</v>
+      </c>
+      <c r="AI21">
+        <v>1.011486370649751</v>
+      </c>
+      <c r="AJ21">
+        <v>16.80940014741567</v>
+      </c>
+      <c r="AK21">
+        <v>23.46585546642769</v>
+      </c>
+      <c r="AL21">
+        <v>4.645611457950789</v>
+      </c>
+      <c r="AM21">
+        <v>0.5747682678036282</v>
+      </c>
+      <c r="AN21">
+        <v>0.9828255639101754</v>
+      </c>
+      <c r="AO21">
+        <v>1.403421496138801</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Massachusetts</t>
+        </is>
+      </c>
+      <c r="B22">
+        <v>2996.545</v>
+      </c>
+      <c r="C22">
+        <v>9556.314</v>
+      </c>
+      <c r="D22">
+        <v>3.18911079259614</v>
+      </c>
+      <c r="E22">
+        <v>0.8622326558126907</v>
+      </c>
+      <c r="F22">
+        <v>3.079057866998713</v>
+      </c>
+      <c r="G22">
+        <v>877552000</v>
+      </c>
+      <c r="H22">
+        <v>313006000</v>
+      </c>
+      <c r="I22">
+        <v>167507000</v>
+      </c>
+      <c r="J22">
+        <v>1951953000</v>
+      </c>
+      <c r="K22">
+        <v>0.648</v>
+      </c>
+      <c r="L22">
+        <v>62.608</v>
+      </c>
+      <c r="M22">
+        <v>1.2</v>
+      </c>
+      <c r="N22">
+        <v>104.577</v>
+      </c>
+      <c r="O22">
+        <v>15.028</v>
+      </c>
+      <c r="P22">
+        <v>501.822</v>
+      </c>
+      <c r="Q22">
+        <v>465.157</v>
+      </c>
+      <c r="R22">
+        <v>1940.45</v>
+      </c>
+      <c r="S22">
+        <v>10</v>
+      </c>
+      <c r="T22">
+        <v>171</v>
+      </c>
+      <c r="U22">
+        <v>162</v>
+      </c>
+      <c r="V22">
+        <v>1051.55157</v>
+      </c>
+      <c r="W22">
+        <v>29366.47448</v>
+      </c>
+      <c r="X22">
+        <v>23708.79952</v>
+      </c>
+      <c r="Y22">
+        <v>5245</v>
+      </c>
+      <c r="Z22">
+        <v>456</v>
+      </c>
+      <c r="AA22">
+        <v>2658410.27104956</v>
+      </c>
+      <c r="AB22">
+        <v>107479156.2288389</v>
+      </c>
+      <c r="AC22">
+        <v>91829.54850583604</v>
+      </c>
+      <c r="AD22">
+        <v>32753.84211946154</v>
+      </c>
+      <c r="AE22">
+        <v>17528.41105890828</v>
+      </c>
+      <c r="AF22">
+        <v>204257.9387826729</v>
+      </c>
+      <c r="AG22">
+        <v>1.035011500127779</v>
+      </c>
+      <c r="AH22">
+        <v>2.994687359262846</v>
+      </c>
+      <c r="AI22">
+        <v>1.14747984738518</v>
+      </c>
+      <c r="AJ22">
+        <v>23.97160452472365</v>
+      </c>
+      <c r="AK22">
+        <v>40.42986043174042</v>
+      </c>
+      <c r="AL22">
+        <v>8.693994280266921</v>
+      </c>
+      <c r="AM22">
+        <v>0.9509757091608926</v>
+      </c>
+      <c r="AN22">
+        <v>0.5822966598066082</v>
+      </c>
+      <c r="AO22">
+        <v>0.6832906063562681</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Michigan</t>
+        </is>
+      </c>
+      <c r="B23">
+        <v>9648.565999999999</v>
+      </c>
+      <c r="C23">
+        <v>27366.346</v>
+      </c>
+      <c r="D23">
+        <v>2.83631225614252</v>
+      </c>
+      <c r="E23">
+        <v>0.4135879521511567</v>
+      </c>
+      <c r="F23">
+        <v>1.476934594371881</v>
+      </c>
+      <c r="G23">
+        <v>1453437000</v>
+      </c>
+      <c r="H23">
+        <v>379062000</v>
+      </c>
+      <c r="I23">
+        <v>127196000</v>
+      </c>
+      <c r="J23">
+        <v>573504000</v>
+      </c>
+      <c r="K23">
+        <v>16.761</v>
+      </c>
+      <c r="L23">
+        <v>558.102</v>
+      </c>
+      <c r="M23">
+        <v>15.055</v>
+      </c>
+      <c r="N23">
+        <v>2129.91</v>
+      </c>
+      <c r="O23">
+        <v>52.424</v>
+      </c>
+      <c r="P23">
+        <v>672.843</v>
+      </c>
+      <c r="Q23">
+        <v>393.858</v>
+      </c>
+      <c r="R23">
+        <v>2323.23</v>
+      </c>
+      <c r="S23">
+        <v>92</v>
+      </c>
+      <c r="T23">
+        <v>351</v>
+      </c>
+      <c r="U23">
+        <v>638</v>
+      </c>
+      <c r="V23">
+        <v>11172.76279</v>
+      </c>
+      <c r="W23">
+        <v>34137.54162</v>
+      </c>
+      <c r="X23">
+        <v>41236.69051000001</v>
+      </c>
+      <c r="Y23">
+        <v>11284</v>
+      </c>
+      <c r="Z23">
+        <v>1240</v>
+      </c>
+      <c r="AA23">
+        <v>3668549.538787774</v>
+      </c>
+      <c r="AB23">
+        <v>89233970.68796086</v>
+      </c>
+      <c r="AC23">
+        <v>53110.37871113666</v>
+      </c>
+      <c r="AD23">
+        <v>13851.39250961747</v>
+      </c>
+      <c r="AE23">
+        <v>4647.898553939207</v>
+      </c>
+      <c r="AF23">
+        <v>20956.54275510512</v>
+      </c>
+      <c r="AG23">
+        <v>3.00321446617285</v>
+      </c>
+      <c r="AH23">
+        <v>7.791416422553256</v>
+      </c>
+      <c r="AI23">
+        <v>0.7068373781051782</v>
+      </c>
+      <c r="AJ23">
+        <v>16.95303521390478</v>
+      </c>
+      <c r="AK23">
+        <v>24.32404680500706</v>
+      </c>
+      <c r="AL23">
+        <v>10.98901098901099</v>
+      </c>
+      <c r="AM23">
+        <v>0.823431068297119</v>
+      </c>
+      <c r="AN23">
+        <v>1.028193546879079</v>
+      </c>
+      <c r="AO23">
+        <v>1.547165866390959</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Minnesota</t>
+        </is>
+      </c>
+      <c r="B24">
+        <v>11694.497</v>
+      </c>
+      <c r="C24">
+        <v>29175.577</v>
+      </c>
+      <c r="D24">
+        <v>2.494812474619473</v>
+      </c>
+      <c r="E24">
+        <v>0.2009653142421142</v>
+      </c>
+      <c r="F24">
+        <v>0.7176529764206395</v>
+      </c>
+      <c r="G24">
+        <v>1197615000</v>
+      </c>
+      <c r="H24">
+        <v>558585000</v>
+      </c>
+      <c r="I24">
+        <v>181153000</v>
+      </c>
+      <c r="J24">
+        <v>416802000</v>
+      </c>
+      <c r="K24">
+        <v>5.254</v>
+      </c>
+      <c r="L24">
+        <v>588.081</v>
+      </c>
+      <c r="M24">
+        <v>19.284</v>
+      </c>
+      <c r="N24">
+        <v>3453.316</v>
+      </c>
+      <c r="O24">
+        <v>10.405</v>
+      </c>
+      <c r="P24">
+        <v>325.418</v>
+      </c>
+      <c r="Q24">
+        <v>11.356</v>
+      </c>
+      <c r="R24">
+        <v>612.246</v>
+      </c>
+      <c r="S24">
+        <v>67</v>
+      </c>
+      <c r="T24">
+        <v>61</v>
+      </c>
+      <c r="U24">
+        <v>264</v>
+      </c>
+      <c r="V24">
+        <v>9729.46025</v>
+      </c>
+      <c r="W24">
+        <v>15098.5755</v>
+      </c>
+      <c r="X24">
+        <v>26791.40539</v>
+      </c>
+      <c r="Y24">
+        <v>13496</v>
+      </c>
+      <c r="Z24">
+        <v>618</v>
+      </c>
+      <c r="AA24">
+        <v>1671500.36888251</v>
+      </c>
+      <c r="AB24">
+        <v>47676289.1795355</v>
+      </c>
+      <c r="AC24">
+        <v>41048.54550091674</v>
+      </c>
+      <c r="AD24">
+        <v>19145.63677695217</v>
+      </c>
+      <c r="AE24">
+        <v>6209.063148948177</v>
+      </c>
+      <c r="AF24">
+        <v>14285.98995659966</v>
+      </c>
+      <c r="AG24">
+        <v>0.8934143425820593</v>
+      </c>
+      <c r="AH24">
+        <v>3.197426079688277</v>
+      </c>
+      <c r="AI24">
+        <v>0.5584197912962497</v>
+      </c>
+      <c r="AJ24">
+        <v>1.854809994675343</v>
+      </c>
+      <c r="AK24">
+        <v>28.52305034871738</v>
+      </c>
+      <c r="AL24">
+        <v>4.57913455838767</v>
+      </c>
+      <c r="AM24">
+        <v>0.6886301837761246</v>
+      </c>
+      <c r="AN24">
+        <v>0.404011623480639</v>
+      </c>
+      <c r="AO24">
+        <v>0.9853906361274315</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Mississippi</t>
+        </is>
+      </c>
+      <c r="B25">
+        <v>10948.065</v>
+      </c>
+      <c r="C25">
+        <v>28310.191</v>
+      </c>
+      <c r="D25">
+        <v>2.585862524564843</v>
+      </c>
+      <c r="E25">
+        <v>0.1711614026199965</v>
+      </c>
+      <c r="F25">
+        <v>0.6112223420335425</v>
+      </c>
+      <c r="G25">
+        <v>708631000</v>
+      </c>
+      <c r="H25">
+        <v>124291000</v>
+      </c>
+      <c r="I25">
+        <v>60441000</v>
+      </c>
+      <c r="J25">
+        <v>137830000</v>
+      </c>
+      <c r="K25">
+        <v>8.637</v>
+      </c>
+      <c r="L25">
+        <v>578.436</v>
+      </c>
+      <c r="M25">
+        <v>16.197</v>
+      </c>
+      <c r="N25">
+        <v>1783.239</v>
+      </c>
+      <c r="O25">
+        <v>7.931999999999999</v>
+      </c>
+      <c r="P25">
+        <v>253.106</v>
+      </c>
+      <c r="Q25">
+        <v>93.539</v>
+      </c>
+      <c r="R25">
+        <v>952.061</v>
+      </c>
+      <c r="S25">
+        <v>177</v>
+      </c>
+      <c r="T25">
+        <v>138</v>
+      </c>
+      <c r="U25">
+        <v>437</v>
+      </c>
+      <c r="V25">
+        <v>9805.39776</v>
+      </c>
+      <c r="W25">
+        <v>9668.9066</v>
+      </c>
+      <c r="X25">
+        <v>20190.78313</v>
+      </c>
+      <c r="Y25">
+        <v>16788</v>
+      </c>
+      <c r="Z25">
+        <v>1174</v>
+      </c>
+      <c r="AA25">
+        <v>510076.2718614815</v>
+      </c>
+      <c r="AB25">
+        <v>11332135.61212148</v>
+      </c>
+      <c r="AC25">
+        <v>25030.95086854059</v>
+      </c>
+      <c r="AD25">
+        <v>4390.327144030925</v>
+      </c>
+      <c r="AE25">
+        <v>2134.955571299396</v>
+      </c>
+      <c r="AF25">
+        <v>4868.564821763301</v>
+      </c>
+      <c r="AG25">
+        <v>1.493164325871834</v>
+      </c>
+      <c r="AH25">
+        <v>3.133864862942799</v>
+      </c>
+      <c r="AI25">
+        <v>0.9082910367034368</v>
+      </c>
+      <c r="AJ25">
+        <v>9.82489567370158</v>
+      </c>
+      <c r="AK25">
+        <v>22.21655120471647</v>
+      </c>
+      <c r="AL25">
+        <v>6.993090302597094</v>
+      </c>
+      <c r="AM25">
+        <v>1.805128199103266</v>
+      </c>
+      <c r="AN25">
+        <v>1.427255487192316</v>
+      </c>
+      <c r="AO25">
+        <v>2.164353889526424</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Missouri</t>
+        </is>
+      </c>
+      <c r="B26">
+        <v>33830.168</v>
+      </c>
+      <c r="C26">
+        <v>77693.084</v>
+      </c>
+      <c r="D26">
+        <v>2.296562169008443</v>
+      </c>
+      <c r="E26">
+        <v>0.1443163718407677</v>
+      </c>
+      <c r="F26">
+        <v>0.5153579571098484</v>
+      </c>
+      <c r="G26">
+        <v>805193000</v>
+      </c>
+      <c r="H26">
+        <v>513233000</v>
+      </c>
+      <c r="I26">
+        <v>182531000</v>
+      </c>
+      <c r="J26">
+        <v>656786000</v>
+      </c>
+      <c r="K26">
+        <v>4.626</v>
+      </c>
+      <c r="L26">
+        <v>841.5349999999999</v>
+      </c>
+      <c r="M26">
+        <v>8.833</v>
+      </c>
+      <c r="N26">
+        <v>1890.406</v>
+      </c>
+      <c r="O26">
+        <v>16.286</v>
+      </c>
+      <c r="P26">
+        <v>538.11</v>
+      </c>
+      <c r="Q26">
+        <v>70.63800000000001</v>
+      </c>
+      <c r="R26">
+        <v>871.4919999999998</v>
+      </c>
+      <c r="S26">
+        <v>146</v>
+      </c>
+      <c r="T26">
+        <v>291</v>
+      </c>
+      <c r="U26">
+        <v>550</v>
+      </c>
+      <c r="V26">
+        <v>14354.89963</v>
+      </c>
+      <c r="W26">
+        <v>22357.05028</v>
+      </c>
+      <c r="X26">
+        <v>36085.08706</v>
+      </c>
+      <c r="Y26">
+        <v>24590</v>
+      </c>
+      <c r="Z26">
+        <v>2218</v>
+      </c>
+      <c r="AA26">
+        <v>1842634.797723567</v>
+      </c>
+      <c r="AB26">
+        <v>51703714.91737627</v>
+      </c>
+      <c r="AC26">
+        <v>10363.76674145153</v>
+      </c>
+      <c r="AD26">
+        <v>6605.903300221677</v>
+      </c>
+      <c r="AE26">
+        <v>2349.385435645726</v>
+      </c>
+      <c r="AF26">
+        <v>8453.596719110803</v>
+      </c>
+      <c r="AG26">
+        <v>0.5497097565757814</v>
+      </c>
+      <c r="AH26">
+        <v>3.02651874152125</v>
+      </c>
+      <c r="AI26">
+        <v>0.4672541242463259</v>
+      </c>
+      <c r="AJ26">
+        <v>8.105410032450099</v>
+      </c>
+      <c r="AK26">
+        <v>28.05966487838622</v>
+      </c>
+      <c r="AL26">
+        <v>9.019926799511998</v>
+      </c>
+      <c r="AM26">
+        <v>1.017074335336192</v>
+      </c>
+      <c r="AN26">
+        <v>1.301602833806393</v>
+      </c>
+      <c r="AO26">
+        <v>1.52417534447262</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Montana</t>
+        </is>
+      </c>
+      <c r="B27">
+        <v>11025.544</v>
+      </c>
+      <c r="C27">
+        <v>25210.881</v>
+      </c>
+      <c r="D27">
+        <v>2.286588398722095</v>
+      </c>
+      <c r="E27">
+        <v>0.06134537702192953</v>
+      </c>
+      <c r="F27">
+        <v>0.2190661238008217</v>
+      </c>
+      <c r="G27">
+        <v>528455000</v>
+      </c>
+      <c r="H27">
+        <v>134321000</v>
+      </c>
+      <c r="I27">
+        <v>44141000</v>
+      </c>
+      <c r="J27">
+        <v>77199000</v>
+      </c>
+      <c r="K27">
+        <v>14.5</v>
+      </c>
+      <c r="L27">
+        <v>1095.069</v>
+      </c>
+      <c r="M27">
+        <v>43.36</v>
+      </c>
+      <c r="N27">
+        <v>2772.977</v>
+      </c>
+      <c r="O27">
+        <v>1.7</v>
+      </c>
+      <c r="P27">
+        <v>97.708</v>
+      </c>
+      <c r="Q27">
+        <v>38.067</v>
+      </c>
+      <c r="R27">
+        <v>255.623</v>
+      </c>
+      <c r="S27">
+        <v>90</v>
+      </c>
+      <c r="T27">
+        <v>14</v>
+      </c>
+      <c r="U27">
+        <v>108</v>
+      </c>
+      <c r="V27">
+        <v>4904.2479</v>
+      </c>
+      <c r="W27">
+        <v>1779.6028</v>
+      </c>
+      <c r="X27">
+        <v>5420.24064</v>
+      </c>
+      <c r="Y27">
+        <v>5266</v>
+      </c>
+      <c r="Z27">
+        <v>365</v>
+      </c>
+      <c r="AA27">
+        <v>158000</v>
+      </c>
+      <c r="AB27">
+        <v>1270000</v>
+      </c>
+      <c r="AC27">
+        <v>20961.3856810478</v>
+      </c>
+      <c r="AD27">
+        <v>5327.897902496941</v>
+      </c>
+      <c r="AE27">
+        <v>1750.870983048946</v>
+      </c>
+      <c r="AF27">
+        <v>3062.130196878086</v>
+      </c>
+      <c r="AG27">
+        <v>1.324117475702445</v>
+      </c>
+      <c r="AH27">
+        <v>1.739878003848201</v>
+      </c>
+      <c r="AI27">
+        <v>1.563662446533094</v>
+      </c>
+      <c r="AJ27">
+        <v>14.89185245459133</v>
+      </c>
+      <c r="AK27">
+        <v>8.037974683544304</v>
+      </c>
+      <c r="AL27">
+        <v>6.931257121154577</v>
+      </c>
+      <c r="AM27">
+        <v>1.835143774033119</v>
+      </c>
+      <c r="AN27">
+        <v>0.7866924012481886</v>
+      </c>
+      <c r="AO27">
+        <v>1.992531460743411</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Nebraska</t>
+        </is>
+      </c>
+      <c r="B28">
+        <v>9939.26</v>
+      </c>
+      <c r="C28">
+        <v>22540.86</v>
+      </c>
+      <c r="D28">
+        <v>2.267860987638919</v>
+      </c>
+      <c r="E28">
+        <v>0.08320977992853866</v>
+      </c>
+      <c r="F28">
+        <v>0.2971445418739238</v>
+      </c>
+      <c r="G28">
+        <v>483546000</v>
+      </c>
+      <c r="H28">
+        <v>224838000</v>
+      </c>
+      <c r="I28">
+        <v>19203000</v>
+      </c>
+      <c r="J28">
+        <v>88435000</v>
+      </c>
+      <c r="K28">
+        <v>2.56</v>
+      </c>
+      <c r="L28">
+        <v>414.6</v>
+      </c>
+      <c r="M28">
+        <v>33.22</v>
+      </c>
+      <c r="N28">
+        <v>2337.734</v>
+      </c>
+      <c r="O28">
+        <v>2.65</v>
+      </c>
+      <c r="P28">
+        <v>68.83</v>
+      </c>
+      <c r="Q28">
+        <v>91.03</v>
+      </c>
+      <c r="R28">
+        <v>317.192</v>
+      </c>
+      <c r="S28">
+        <v>71</v>
+      </c>
+      <c r="T28">
+        <v>37</v>
+      </c>
+      <c r="U28">
+        <v>125</v>
+      </c>
+      <c r="V28">
+        <v>5794.80081</v>
+      </c>
+      <c r="W28">
+        <v>4409.643110000001</v>
+      </c>
+      <c r="X28">
+        <v>9227.42078</v>
+      </c>
+      <c r="Y28">
+        <v>15348</v>
+      </c>
+      <c r="Z28">
+        <v>1280</v>
+      </c>
+      <c r="AA28">
+        <v>573578.0225506546</v>
+      </c>
+      <c r="AB28">
+        <v>8412472.086883757</v>
+      </c>
+      <c r="AC28">
+        <v>21451.97654392956</v>
+      </c>
+      <c r="AD28">
+        <v>9974.685970277975</v>
+      </c>
+      <c r="AE28">
+        <v>851.9195807081007</v>
+      </c>
+      <c r="AF28">
+        <v>3923.319695876732</v>
+      </c>
+      <c r="AG28">
+        <v>0.6174626145682586</v>
+      </c>
+      <c r="AH28">
+        <v>3.850065378468691</v>
+      </c>
+      <c r="AI28">
+        <v>1.421034215184448</v>
+      </c>
+      <c r="AJ28">
+        <v>28.69870614643497</v>
+      </c>
+      <c r="AK28">
+        <v>14.66665694315515</v>
+      </c>
+      <c r="AL28">
+        <v>8.339848840239771</v>
+      </c>
+      <c r="AM28">
+        <v>1.22523624759416</v>
+      </c>
+      <c r="AN28">
+        <v>0.8390701713726668</v>
+      </c>
+      <c r="AO28">
+        <v>1.354658067300145</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Nevada</t>
+        </is>
+      </c>
+      <c r="B29">
+        <v>5354.476</v>
+      </c>
+      <c r="C29">
+        <v>13508.747</v>
+      </c>
+      <c r="D29">
+        <v>2.522888700967191</v>
+      </c>
+      <c r="E29">
+        <v>0.2082556583523254</v>
+      </c>
+      <c r="F29">
+        <v>0.7436870070669455</v>
+      </c>
+      <c r="G29">
+        <v>690578000</v>
+      </c>
+      <c r="H29">
+        <v>156288000</v>
+      </c>
+      <c r="I29">
+        <v>183901000</v>
+      </c>
+      <c r="J29">
+        <v>185334000</v>
+      </c>
+      <c r="K29">
+        <v>0.8</v>
+      </c>
+      <c r="L29">
+        <v>456.673</v>
+      </c>
+      <c r="M29">
+        <v>1.746</v>
+      </c>
+      <c r="N29">
+        <v>1519.397</v>
+      </c>
+      <c r="O29">
+        <v>4</v>
+      </c>
+      <c r="P29">
+        <v>161.598</v>
+      </c>
+      <c r="Q29">
+        <v>19.047</v>
+      </c>
+      <c r="R29">
+        <v>378.161</v>
+      </c>
+      <c r="S29">
+        <v>84</v>
+      </c>
+      <c r="T29">
+        <v>94</v>
+      </c>
+      <c r="U29">
+        <v>139</v>
+      </c>
+      <c r="V29">
+        <v>3843.86286</v>
+      </c>
+      <c r="W29">
+        <v>8699.340620000001</v>
+      </c>
+      <c r="X29">
+        <v>12688.14289</v>
+      </c>
+      <c r="Y29">
+        <v>2067</v>
+      </c>
+      <c r="Z29">
+        <v>29</v>
+      </c>
+      <c r="AA29">
+        <v>1338000</v>
+      </c>
+      <c r="AB29">
+        <v>21934000</v>
+      </c>
+      <c r="AC29">
+        <v>51120.80343202815</v>
+      </c>
+      <c r="AD29">
+        <v>11569.39277935992</v>
+      </c>
+      <c r="AE29">
+        <v>13613.47577240139</v>
+      </c>
+      <c r="AF29">
+        <v>13719.55518894536</v>
+      </c>
+      <c r="AG29">
+        <v>0.1751800522474506</v>
+      </c>
+      <c r="AH29">
+        <v>2.47527815938316</v>
+      </c>
+      <c r="AI29">
+        <v>0.114914008649484</v>
+      </c>
+      <c r="AJ29">
+        <v>5.036743609203487</v>
+      </c>
+      <c r="AK29">
+        <v>16.3931240657698</v>
+      </c>
+      <c r="AL29">
+        <v>1.402999516207063</v>
+      </c>
+      <c r="AM29">
+        <v>2.185301688936946</v>
+      </c>
+      <c r="AN29">
+        <v>1.080541665237152</v>
+      </c>
+      <c r="AO29">
+        <v>1.095510991679887</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>New Hampshire</t>
+        </is>
+      </c>
+      <c r="B30">
+        <v>3896.922</v>
+      </c>
+      <c r="C30">
+        <v>8453.163</v>
+      </c>
+      <c r="D30">
+        <v>2.169189683550248</v>
+      </c>
+      <c r="E30">
+        <v>0.2080343180416608</v>
+      </c>
+      <c r="F30">
+        <v>0.7428965943862831</v>
+      </c>
+      <c r="G30">
+        <v>273146000</v>
+      </c>
+      <c r="H30">
+        <v>110295000</v>
+      </c>
+      <c r="I30">
+        <v>109401000</v>
+      </c>
+      <c r="J30">
+        <v>106926000</v>
+      </c>
+      <c r="K30">
+        <v>0.5</v>
+      </c>
+      <c r="L30">
+        <v>141.961</v>
+      </c>
+      <c r="M30">
+        <v>2.853</v>
+      </c>
+      <c r="N30">
+        <v>322.742</v>
+      </c>
+      <c r="O30">
+        <v>0.131</v>
+      </c>
+      <c r="P30">
+        <v>83.04600000000001</v>
+      </c>
+      <c r="Q30">
+        <v>12.597</v>
+      </c>
+      <c r="R30">
+        <v>223.028</v>
+      </c>
+      <c r="S30">
+        <v>16</v>
+      </c>
+      <c r="T30">
+        <v>15</v>
+      </c>
+      <c r="U30">
+        <v>71</v>
+      </c>
+      <c r="V30">
+        <v>2078.74883</v>
+      </c>
+      <c r="W30">
+        <v>4072.969160000001</v>
+      </c>
+      <c r="X30">
+        <v>5804.53779</v>
+      </c>
+      <c r="Y30">
+        <v>2527</v>
+      </c>
+      <c r="Z30">
+        <v>194</v>
+      </c>
+      <c r="AA30">
+        <v>377713.7507341292</v>
+      </c>
+      <c r="AB30">
+        <v>7226966.175081165</v>
+      </c>
+      <c r="AC30">
+        <v>32312.87507409948</v>
+      </c>
+      <c r="AD30">
+        <v>13047.77868355313</v>
+      </c>
+      <c r="AE30">
+        <v>12942.01945472955</v>
+      </c>
+      <c r="AF30">
+        <v>12649.22964338911</v>
+      </c>
+      <c r="AG30">
+        <v>0.3522094096265875</v>
+      </c>
+      <c r="AH30">
+        <v>0.1577439009705464</v>
+      </c>
+      <c r="AI30">
+        <v>0.8839878292877903</v>
+      </c>
+      <c r="AJ30">
+        <v>5.648169736535323</v>
+      </c>
+      <c r="AK30">
+        <v>19.1334473818725</v>
+      </c>
+      <c r="AL30">
+        <v>7.677087455480808</v>
+      </c>
+      <c r="AM30">
+        <v>0.7696937585287781</v>
+      </c>
+      <c r="AN30">
+        <v>0.3682816984550896</v>
+      </c>
+      <c r="AO30">
+        <v>1.223180941681835</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>New Jersey</t>
+        </is>
+      </c>
+      <c r="B31">
+        <v>2329.06</v>
+      </c>
+      <c r="C31">
+        <v>8551.253000000001</v>
+      </c>
+      <c r="D31">
+        <v>3.671546890161697</v>
+      </c>
+      <c r="E31">
+        <v>0.8905239968926189</v>
+      </c>
+      <c r="F31">
+        <v>3.180087068030297</v>
+      </c>
+      <c r="G31">
+        <v>2944934000</v>
+      </c>
+      <c r="H31">
+        <v>742395000</v>
+      </c>
+      <c r="I31">
+        <v>173908000</v>
+      </c>
+      <c r="J31">
+        <v>5868512000</v>
+      </c>
+      <c r="K31">
+        <v>0.5800000000000001</v>
+      </c>
+      <c r="L31">
+        <v>44.88</v>
+      </c>
+      <c r="M31">
+        <v>3.61</v>
+      </c>
+      <c r="N31">
+        <v>159.64</v>
+      </c>
+      <c r="O31">
+        <v>36.03</v>
+      </c>
+      <c r="P31">
+        <v>386.66</v>
+      </c>
+      <c r="Q31">
+        <v>336.2</v>
+      </c>
+      <c r="R31">
+        <v>1798.98</v>
+      </c>
+      <c r="S31">
+        <v>18</v>
+      </c>
+      <c r="T31">
+        <v>329</v>
+      </c>
+      <c r="U31">
+        <v>224</v>
+      </c>
+      <c r="V31">
+        <v>1995.25338</v>
+      </c>
+      <c r="W31">
+        <v>37594.85838</v>
+      </c>
+      <c r="X31">
+        <v>26751.0382</v>
+      </c>
+      <c r="Y31">
+        <v>6798</v>
+      </c>
+      <c r="Z31">
+        <v>482</v>
+      </c>
+      <c r="AA31">
+        <v>4147574.647293678</v>
+      </c>
+      <c r="AB31">
+        <v>199091988.3769594</v>
+      </c>
+      <c r="AC31">
+        <v>344386.2554411616</v>
+      </c>
+      <c r="AD31">
+        <v>86817.10154055785</v>
+      </c>
+      <c r="AE31">
+        <v>20337.13655764833</v>
+      </c>
+      <c r="AF31">
+        <v>686275.099099512</v>
+      </c>
+      <c r="AG31">
+        <v>1.292335115864528</v>
+      </c>
+      <c r="AH31">
+        <v>9.318264108001861</v>
+      </c>
+      <c r="AI31">
+        <v>2.261338010523678</v>
+      </c>
+      <c r="AJ31">
+        <v>18.68836785289442</v>
+      </c>
+      <c r="AK31">
+        <v>48.00202655951432</v>
+      </c>
+      <c r="AL31">
+        <v>7.090320682553693</v>
+      </c>
+      <c r="AM31">
+        <v>0.9021410604000581</v>
+      </c>
+      <c r="AN31">
+        <v>0.8751196684252545</v>
+      </c>
+      <c r="AO31">
+        <v>0.8373506789729005</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>New Mexico</t>
+        </is>
+      </c>
+      <c r="B32">
+        <v>11920.879</v>
+      </c>
+      <c r="C32">
+        <v>29429.545</v>
+      </c>
+      <c r="D32">
+        <v>2.468739511574607</v>
+      </c>
+      <c r="E32">
+        <v>0.1163472625893469</v>
+      </c>
+      <c r="F32">
+        <v>0.4154794553006546</v>
+      </c>
+      <c r="G32">
+        <v>435393000</v>
+      </c>
+      <c r="H32">
+        <v>52738000</v>
+      </c>
+      <c r="I32">
+        <v>314077000</v>
+      </c>
+      <c r="J32">
+        <v>172809000</v>
+      </c>
+      <c r="K32">
+        <v>23.696</v>
+      </c>
+      <c r="L32">
+        <v>843.336</v>
+      </c>
+      <c r="M32">
+        <v>24.221</v>
+      </c>
+      <c r="N32">
+        <v>1915.734</v>
+      </c>
+      <c r="O32">
+        <v>5.577</v>
+      </c>
+      <c r="P32">
+        <v>156.087</v>
+      </c>
+      <c r="Q32">
+        <v>99.315</v>
+      </c>
+      <c r="R32">
+        <v>700.479</v>
+      </c>
+      <c r="S32">
+        <v>95</v>
+      </c>
+      <c r="T32">
+        <v>134</v>
+      </c>
+      <c r="U32">
+        <v>166</v>
+      </c>
+      <c r="V32">
+        <v>7377.0226</v>
+      </c>
+      <c r="W32">
+        <v>6224.00848</v>
+      </c>
+      <c r="X32">
+        <v>10155.40451</v>
+      </c>
+      <c r="Y32">
+        <v>4025</v>
+      </c>
+      <c r="Z32">
+        <v>208</v>
+      </c>
+      <c r="AA32">
+        <v>601527.8010158264</v>
+      </c>
+      <c r="AB32">
+        <v>10614889.63250645</v>
+      </c>
+      <c r="AC32">
+        <v>14794.41833028679</v>
+      </c>
+      <c r="AD32">
+        <v>1792.008676994497</v>
+      </c>
+      <c r="AE32">
+        <v>10672.16635527325</v>
+      </c>
+      <c r="AF32">
+        <v>5871.956226302514</v>
+      </c>
+      <c r="AG32">
+        <v>2.809793486819014</v>
+      </c>
+      <c r="AH32">
+        <v>3.573007361279287</v>
+      </c>
+      <c r="AI32">
+        <v>1.264319576726205</v>
+      </c>
+      <c r="AJ32">
+        <v>14.17815523377574</v>
+      </c>
+      <c r="AK32">
+        <v>17.64654869580527</v>
+      </c>
+      <c r="AL32">
+        <v>5.167701863354037</v>
+      </c>
+      <c r="AM32">
+        <v>1.287782417800916</v>
+      </c>
+      <c r="AN32">
+        <v>2.152953364870736</v>
+      </c>
+      <c r="AO32">
+        <v>1.634597615846225</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="B33">
+        <v>15095.98</v>
+      </c>
+      <c r="C33">
+        <v>38156.8</v>
+      </c>
+      <c r="D33">
+        <v>2.52761331162336</v>
+      </c>
+      <c r="E33">
+        <v>0.4432211296544784</v>
+      </c>
+      <c r="F33">
+        <v>1.582755532259895</v>
+      </c>
+      <c r="G33">
+        <v>3937980000</v>
+      </c>
+      <c r="H33">
+        <v>1920550000</v>
+      </c>
+      <c r="I33">
+        <v>464851000</v>
+      </c>
+      <c r="J33">
+        <v>7983023000</v>
+      </c>
+      <c r="K33">
+        <v>21.81</v>
+      </c>
+      <c r="L33">
+        <v>797.9299999999998</v>
+      </c>
+      <c r="M33">
+        <v>26.25</v>
+      </c>
+      <c r="N33">
+        <v>2071.8</v>
+      </c>
+      <c r="O33">
+        <v>86.62</v>
+      </c>
+      <c r="P33">
+        <v>922.53</v>
+      </c>
+      <c r="Q33">
+        <v>731.15</v>
+      </c>
+      <c r="R33">
+        <v>3070.69</v>
+      </c>
+      <c r="S33">
+        <v>70</v>
+      </c>
+      <c r="T33">
+        <v>425</v>
+      </c>
+      <c r="U33">
+        <v>551</v>
+      </c>
+      <c r="V33">
+        <v>8479.54888</v>
+      </c>
+      <c r="W33">
+        <v>46886.94953</v>
+      </c>
+      <c r="X33">
+        <v>47110.37613</v>
+      </c>
+      <c r="Y33">
+        <v>17555</v>
+      </c>
+      <c r="Z33">
+        <v>1672</v>
+      </c>
+      <c r="AA33">
+        <v>4965924.86009466</v>
+      </c>
+      <c r="AB33">
+        <v>214395519.6869412</v>
+      </c>
+      <c r="AC33">
+        <v>103205.1954042268</v>
+      </c>
+      <c r="AD33">
+        <v>50333.09921167393</v>
+      </c>
+      <c r="AE33">
+        <v>12182.65158503858</v>
+      </c>
+      <c r="AF33">
+        <v>209216.2602733982</v>
+      </c>
+      <c r="AG33">
+        <v>2.733322471896032</v>
+      </c>
+      <c r="AH33">
+        <v>9.389396550789678</v>
+      </c>
+      <c r="AI33">
+        <v>1.267014190558934</v>
+      </c>
+      <c r="AJ33">
+        <v>23.8106093418743</v>
+      </c>
+      <c r="AK33">
+        <v>43.17333139890773</v>
+      </c>
+      <c r="AL33">
+        <v>9.52435203645685</v>
+      </c>
+      <c r="AM33">
+        <v>0.8255156139862949</v>
+      </c>
+      <c r="AN33">
+        <v>0.9064355951074816</v>
+      </c>
+      <c r="AO33">
+        <v>1.169593718546267</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>North Carolina</t>
+        </is>
+      </c>
+      <c r="B34">
+        <v>80211.66499999999</v>
+      </c>
+      <c r="C34">
+        <v>173653.322</v>
+      </c>
+      <c r="D34">
+        <v>2.164938503645324</v>
+      </c>
+      <c r="E34">
+        <v>0.2888483008692457</v>
+      </c>
+      <c r="F34">
+        <v>1.031485675200255</v>
+      </c>
+      <c r="G34">
+        <v>4844323000</v>
+      </c>
+      <c r="H34">
+        <v>1272829000</v>
+      </c>
+      <c r="I34">
+        <v>374775000</v>
+      </c>
+      <c r="J34">
+        <v>649689000</v>
+      </c>
+      <c r="K34">
+        <v>4.205</v>
+      </c>
+      <c r="L34">
+        <v>544.043</v>
+      </c>
+      <c r="M34">
+        <v>6.479</v>
+      </c>
+      <c r="N34">
+        <v>1595.917</v>
+      </c>
+      <c r="O34">
+        <v>17.701</v>
+      </c>
+      <c r="P34">
+        <v>780.311</v>
+      </c>
+      <c r="Q34">
+        <v>82.26999999999998</v>
+      </c>
+      <c r="R34">
+        <v>1977.291</v>
+      </c>
+      <c r="S34">
+        <v>163</v>
+      </c>
+      <c r="T34">
+        <v>339</v>
+      </c>
+      <c r="U34">
+        <v>1029</v>
+      </c>
+      <c r="V34">
+        <v>14101.33355</v>
+      </c>
+      <c r="W34">
+        <v>36554.73714</v>
+      </c>
+      <c r="X34">
+        <v>55686.29467</v>
+      </c>
+      <c r="Y34">
+        <v>18877</v>
+      </c>
+      <c r="Z34">
+        <v>1325</v>
+      </c>
+      <c r="AA34">
+        <v>3152545.002976113</v>
+      </c>
+      <c r="AB34">
+        <v>51597688.13740633</v>
+      </c>
+      <c r="AC34">
+        <v>27896.5178679392</v>
+      </c>
+      <c r="AD34">
+        <v>7329.712932298526</v>
+      </c>
+      <c r="AE34">
+        <v>2158.179271687069</v>
+      </c>
+      <c r="AF34">
+        <v>3741.299000315123</v>
+      </c>
+      <c r="AG34">
+        <v>0.7729168466463129</v>
+      </c>
+      <c r="AH34">
+        <v>2.268454500833642</v>
+      </c>
+      <c r="AI34">
+        <v>0.4059734936090035</v>
+      </c>
+      <c r="AJ34">
+        <v>4.160743158189663</v>
+      </c>
+      <c r="AK34">
+        <v>16.36699494811218</v>
+      </c>
+      <c r="AL34">
+        <v>7.019123801451502</v>
+      </c>
+      <c r="AM34">
+        <v>1.155919044266562</v>
+      </c>
+      <c r="AN34">
+        <v>0.9273763854508735</v>
+      </c>
+      <c r="AO34">
+        <v>1.847851443695275</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>North Dakota</t>
+        </is>
+      </c>
+      <c r="B35">
+        <v>7411.548</v>
+      </c>
+      <c r="C35">
+        <v>17245.396</v>
+      </c>
+      <c r="D35">
+        <v>2.326827809790883</v>
+      </c>
+      <c r="E35">
+        <v>0.05093023088597096</v>
+      </c>
+      <c r="F35">
+        <v>0.1818733343261082</v>
+      </c>
+      <c r="G35">
+        <v>376287000</v>
+      </c>
+      <c r="H35">
+        <v>30940000</v>
+      </c>
+      <c r="I35">
+        <v>20294000</v>
+      </c>
+      <c r="J35">
+        <v>36915000</v>
+      </c>
+      <c r="K35">
+        <v>1.949</v>
+      </c>
+      <c r="L35">
+        <v>509.732</v>
+      </c>
+      <c r="M35">
+        <v>32.575</v>
+      </c>
+      <c r="N35">
+        <v>2944.629</v>
+      </c>
+      <c r="O35">
+        <v>0.6</v>
+      </c>
+      <c r="P35">
+        <v>61.191</v>
+      </c>
+      <c r="Q35">
+        <v>17.905</v>
+      </c>
+      <c r="R35">
+        <v>206.875</v>
+      </c>
+      <c r="S35">
+        <v>33</v>
+      </c>
+      <c r="T35">
+        <v>7</v>
+      </c>
+      <c r="U35">
+        <v>60</v>
+      </c>
+      <c r="V35">
+        <v>3184.75673</v>
+      </c>
+      <c r="W35">
+        <v>1312.67259</v>
+      </c>
+      <c r="X35">
+        <v>4270.17145</v>
+      </c>
+      <c r="Y35">
+        <v>4285</v>
+      </c>
+      <c r="Z35">
+        <v>481</v>
+      </c>
+      <c r="AA35">
+        <v>179574.3505681844</v>
+      </c>
+      <c r="AB35">
+        <v>1540594.804545475</v>
+      </c>
+      <c r="AC35">
+        <v>21819.56274010756</v>
+      </c>
+      <c r="AD35">
+        <v>1794.102031637893</v>
+      </c>
+      <c r="AE35">
+        <v>1176.77784841821</v>
+      </c>
+      <c r="AF35">
+        <v>2140.571315381798</v>
+      </c>
+      <c r="AG35">
+        <v>0.3823577880140936</v>
+      </c>
+      <c r="AH35">
+        <v>0.9805363533853017</v>
+      </c>
+      <c r="AI35">
+        <v>1.106251415713151</v>
+      </c>
+      <c r="AJ35">
+        <v>8.654984894259819</v>
+      </c>
+      <c r="AK35">
+        <v>8.579147298436204</v>
+      </c>
+      <c r="AL35">
+        <v>11.22520420070012</v>
+      </c>
+      <c r="AM35">
+        <v>1.036185894173462</v>
+      </c>
+      <c r="AN35">
+        <v>0.5332632107447296</v>
+      </c>
+      <c r="AO35">
+        <v>1.40509580710161</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Ohio</t>
+        </is>
+      </c>
+      <c r="B36">
+        <v>19257.183</v>
+      </c>
+      <c r="C36">
+        <v>49680.663</v>
+      </c>
+      <c r="D36">
+        <v>2.579851009361026</v>
+      </c>
+      <c r="E36">
+        <v>0.3856877674921528</v>
+      </c>
+      <c r="F36">
+        <v>1.377302224284886</v>
+      </c>
+      <c r="G36">
+        <v>1970380000</v>
+      </c>
+      <c r="H36">
+        <v>480042000</v>
+      </c>
+      <c r="I36">
+        <v>612521000</v>
+      </c>
+      <c r="J36">
+        <v>927812000</v>
+      </c>
+      <c r="K36">
+        <v>13.97</v>
+      </c>
+      <c r="L36">
+        <v>642.63</v>
+      </c>
+      <c r="M36">
+        <v>9.448</v>
+      </c>
+      <c r="N36">
+        <v>1521.871</v>
+      </c>
+      <c r="O36">
+        <v>42.474</v>
+      </c>
+      <c r="P36">
+        <v>930.684</v>
+      </c>
+      <c r="Q36">
+        <v>368.538</v>
+      </c>
+      <c r="R36">
+        <v>2398.031</v>
+      </c>
+      <c r="S36">
+        <v>112</v>
+      </c>
+      <c r="T36">
+        <v>323</v>
+      </c>
+      <c r="U36">
+        <v>763</v>
+      </c>
+      <c r="V36">
+        <v>13185.06909</v>
+      </c>
+      <c r="W36">
+        <v>38928.38958</v>
+      </c>
+      <c r="X36">
+        <v>51001.47745999999</v>
+      </c>
+      <c r="Y36">
+        <v>27151</v>
+      </c>
+      <c r="Z36">
+        <v>1334</v>
+      </c>
+      <c r="AA36">
+        <v>4026880.106658366</v>
+      </c>
+      <c r="AB36">
+        <v>90964941.32544281</v>
+      </c>
+      <c r="AC36">
+        <v>39660.90388125456</v>
+      </c>
+      <c r="AD36">
+        <v>9662.552208693351</v>
+      </c>
+      <c r="AE36">
+        <v>12329.16315951742</v>
+      </c>
+      <c r="AF36">
+        <v>18675.5156629049</v>
+      </c>
+      <c r="AG36">
+        <v>2.173879215100447</v>
+      </c>
+      <c r="AH36">
+        <v>4.563740216872753</v>
+      </c>
+      <c r="AI36">
+        <v>0.6208147733940655</v>
+      </c>
+      <c r="AJ36">
+        <v>15.36835845741777</v>
+      </c>
+      <c r="AK36">
+        <v>22.589433734328</v>
+      </c>
+      <c r="AL36">
+        <v>4.913262863246289</v>
+      </c>
+      <c r="AM36">
+        <v>0.8494456815925566</v>
+      </c>
+      <c r="AN36">
+        <v>0.8297286465863609</v>
+      </c>
+      <c r="AO36">
+        <v>1.496035091529288</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Oklahoma</t>
+        </is>
+      </c>
+      <c r="B37">
+        <v>12252.49</v>
+      </c>
+      <c r="C37">
+        <v>30406.567</v>
+      </c>
+      <c r="D37">
+        <v>2.481664298440561</v>
+      </c>
+      <c r="E37">
+        <v>0.174813552611842</v>
+      </c>
+      <c r="F37">
+        <v>0.6242642757715455</v>
+      </c>
+      <c r="G37">
+        <v>1360030000</v>
+      </c>
+      <c r="H37">
+        <v>703103000</v>
+      </c>
+      <c r="I37">
+        <v>247262000</v>
+      </c>
+      <c r="J37">
+        <v>384361000</v>
+      </c>
+      <c r="K37">
+        <v>15</v>
+      </c>
+      <c r="L37">
+        <v>636.72</v>
+      </c>
+      <c r="M37">
+        <v>45.799</v>
+      </c>
+      <c r="N37">
+        <v>2236.102</v>
+      </c>
+      <c r="O37">
+        <v>15.398</v>
+      </c>
+      <c r="P37">
+        <v>284.13</v>
+      </c>
+      <c r="Q37">
+        <v>71.303</v>
+      </c>
+      <c r="R37">
+        <v>738.818</v>
+      </c>
+      <c r="S37">
+        <v>134</v>
+      </c>
+      <c r="T37">
+        <v>149</v>
+      </c>
+      <c r="U37">
+        <v>369</v>
+      </c>
+      <c r="V37">
+        <v>10066.36018</v>
+      </c>
+      <c r="W37">
+        <v>13168.33508</v>
+      </c>
+      <c r="X37">
+        <v>18765.48327</v>
+      </c>
+      <c r="Y37">
+        <v>23220</v>
+      </c>
+      <c r="Z37">
+        <v>2296</v>
+      </c>
+      <c r="AA37">
+        <v>1078489.624732343</v>
+      </c>
+      <c r="AB37">
+        <v>31972406.62259109</v>
+      </c>
+      <c r="AC37">
+        <v>44728.16678055106</v>
+      </c>
+      <c r="AD37">
+        <v>23123.39304861348</v>
+      </c>
+      <c r="AE37">
+        <v>8131.861778411223</v>
+      </c>
+      <c r="AF37">
+        <v>12640.72330164731</v>
+      </c>
+      <c r="AG37">
+        <v>2.355823595929137</v>
+      </c>
+      <c r="AH37">
+        <v>5.419350297399078</v>
+      </c>
+      <c r="AI37">
+        <v>2.048162382574677</v>
+      </c>
+      <c r="AJ37">
+        <v>9.65095598645404</v>
+      </c>
+      <c r="AK37">
+        <v>29.64553936300122</v>
+      </c>
+      <c r="AL37">
+        <v>9.888027562446167</v>
+      </c>
+      <c r="AM37">
+        <v>1.331166356099927</v>
+      </c>
+      <c r="AN37">
+        <v>1.131502191391685</v>
+      </c>
+      <c r="AO37">
+        <v>1.966376216859349</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Oregon</t>
+        </is>
+      </c>
+      <c r="B38">
+        <v>7602.71</v>
+      </c>
+      <c r="C38">
+        <v>18460.35</v>
+      </c>
+      <c r="D38">
+        <v>2.428127601868281</v>
+      </c>
+      <c r="E38">
+        <v>0.2145555203449556</v>
+      </c>
+      <c r="F38">
+        <v>0.766183997291853</v>
+      </c>
+      <c r="G38">
+        <v>924356000</v>
+      </c>
+      <c r="H38">
+        <v>291763000</v>
+      </c>
+      <c r="I38">
+        <v>159947000</v>
+      </c>
+      <c r="J38">
+        <v>625050000</v>
+      </c>
+      <c r="K38">
+        <v>3.24</v>
+      </c>
+      <c r="L38">
+        <v>493.51</v>
+      </c>
+      <c r="M38">
+        <v>19.1</v>
+      </c>
+      <c r="N38">
+        <v>2652.45</v>
+      </c>
+      <c r="O38">
+        <v>6.69</v>
+      </c>
+      <c r="P38">
+        <v>232.69</v>
+      </c>
+      <c r="Q38">
+        <v>64.98999999999999</v>
+      </c>
+      <c r="R38">
+        <v>838.77</v>
+      </c>
+      <c r="S38">
+        <v>124</v>
+      </c>
+      <c r="T38">
+        <v>125</v>
+      </c>
+      <c r="U38">
+        <v>259</v>
+      </c>
+      <c r="V38">
+        <v>7593.10952</v>
+      </c>
+      <c r="W38">
+        <v>11339.38888</v>
+      </c>
+      <c r="X38">
+        <v>13365.48005</v>
+      </c>
+      <c r="Y38">
+        <v>8235</v>
+      </c>
+      <c r="Z38">
+        <v>382</v>
+      </c>
+      <c r="AA38">
+        <v>1244087.842041542</v>
+      </c>
+      <c r="AB38">
+        <v>28638454.14788176</v>
+      </c>
+      <c r="AC38">
+        <v>50072.50675095543</v>
+      </c>
+      <c r="AD38">
+        <v>15804.84660366678</v>
+      </c>
+      <c r="AE38">
+        <v>8664.353601096405</v>
+      </c>
+      <c r="AF38">
+        <v>33859.05467664481</v>
+      </c>
+      <c r="AG38">
+        <v>0.6565216510303743</v>
+      </c>
+      <c r="AH38">
+        <v>2.875069835403327</v>
+      </c>
+      <c r="AI38">
+        <v>0.7200889743444741</v>
+      </c>
+      <c r="AJ38">
+        <v>7.748250414297125</v>
+      </c>
+      <c r="AK38">
+        <v>23.01963991617039</v>
+      </c>
+      <c r="AL38">
+        <v>4.638737097753491</v>
+      </c>
+      <c r="AM38">
+        <v>1.633059547914963</v>
+      </c>
+      <c r="AN38">
+        <v>1.102352175437518</v>
+      </c>
+      <c r="AO38">
+        <v>1.9378278896911</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Pennsylvania</t>
+        </is>
+      </c>
+      <c r="B39">
+        <v>39713.25</v>
+      </c>
+      <c r="C39">
+        <v>88322.133</v>
+      </c>
+      <c r="D39">
+        <v>2.223996600630772</v>
+      </c>
+      <c r="E39">
+        <v>0.3264881635048374</v>
+      </c>
+      <c r="F39">
+        <v>1.165898718338401</v>
+      </c>
+      <c r="G39">
+        <v>3817048000</v>
+      </c>
+      <c r="H39">
+        <v>1794855000</v>
+      </c>
+      <c r="I39">
+        <v>945086000</v>
+      </c>
+      <c r="J39">
+        <v>2474696000</v>
+      </c>
+      <c r="K39">
+        <v>32.283</v>
+      </c>
+      <c r="L39">
+        <v>1066.255</v>
+      </c>
+      <c r="M39">
+        <v>21.288</v>
+      </c>
+      <c r="N39">
+        <v>1578.923</v>
+      </c>
+      <c r="O39">
+        <v>48.862</v>
+      </c>
+      <c r="P39">
+        <v>797.0639999999999</v>
+      </c>
+      <c r="Q39">
+        <v>379.901</v>
+      </c>
+      <c r="R39">
+        <v>2865.955</v>
+      </c>
+      <c r="S39">
+        <v>124</v>
+      </c>
+      <c r="T39">
+        <v>354</v>
+      </c>
+      <c r="U39">
+        <v>645</v>
+      </c>
+      <c r="V39">
+        <v>14889.82588</v>
+      </c>
+      <c r="W39">
+        <v>33384.06472</v>
+      </c>
+      <c r="X39">
+        <v>39708.60034</v>
+      </c>
+      <c r="Y39">
+        <v>23166</v>
+      </c>
+      <c r="Z39">
+        <v>3198</v>
+      </c>
+      <c r="AA39">
+        <v>4113843.061315846</v>
+      </c>
+      <c r="AB39">
+        <v>94284312.15214342</v>
+      </c>
+      <c r="AC39">
+        <v>43217.34394707157</v>
+      </c>
+      <c r="AD39">
+        <v>20321.68992114355</v>
+      </c>
+      <c r="AE39">
+        <v>10700.44356831826</v>
+      </c>
+      <c r="AF39">
+        <v>28018.97911591424</v>
+      </c>
+      <c r="AG39">
+        <v>3.027699752873374</v>
+      </c>
+      <c r="AH39">
+        <v>6.130248010197426</v>
+      </c>
+      <c r="AI39">
+        <v>1.348260808158473</v>
+      </c>
+      <c r="AJ39">
+        <v>13.25565125760872</v>
+      </c>
+      <c r="AK39">
+        <v>22.91879168623069</v>
+      </c>
+      <c r="AL39">
+        <v>13.80471380471381</v>
+      </c>
+      <c r="AM39">
+        <v>0.8327834119709665</v>
+      </c>
+      <c r="AN39">
+        <v>1.060386154199859</v>
+      </c>
+      <c r="AO39">
+        <v>1.62433325394818</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Rhode Island</t>
+        </is>
+      </c>
+      <c r="B40">
+        <v>1104.673</v>
+      </c>
+      <c r="C40">
+        <v>2869.8</v>
+      </c>
+      <c r="D40">
+        <v>2.597872854681883</v>
+      </c>
+      <c r="E40">
+        <v>0.7075479127465328</v>
+      </c>
+      <c r="F40">
+        <v>2.526674154978886</v>
+      </c>
+      <c r="G40">
+        <v>356087000</v>
+      </c>
+      <c r="H40">
+        <v>113401000</v>
+      </c>
+      <c r="I40">
+        <v>35653000</v>
+      </c>
+      <c r="J40">
+        <v>126315000</v>
+      </c>
+      <c r="K40">
+        <v>0.049</v>
+      </c>
+      <c r="L40">
+        <v>17.843</v>
+      </c>
+      <c r="M40">
+        <v>4.132</v>
+      </c>
+      <c r="N40">
+        <v>97.3</v>
+      </c>
+      <c r="O40">
+        <v>1.301</v>
+      </c>
+      <c r="P40">
+        <v>52.166</v>
+      </c>
+      <c r="Q40">
+        <v>102.412</v>
+      </c>
+      <c r="R40">
+        <v>341.337</v>
+      </c>
+      <c r="S40">
+        <v>6</v>
+      </c>
+      <c r="T40">
+        <v>35</v>
+      </c>
+      <c r="U40">
+        <v>26</v>
+      </c>
+      <c r="V40">
+        <v>503.39365</v>
+      </c>
+      <c r="W40">
+        <v>4205.40235</v>
+      </c>
+      <c r="X40">
+        <v>2155.29726</v>
+      </c>
+      <c r="Y40">
+        <v>779</v>
+      </c>
+      <c r="Z40">
+        <v>136</v>
+      </c>
+      <c r="AA40">
+        <v>474398.1037737231</v>
+      </c>
+      <c r="AB40">
+        <v>15498394.94724461</v>
+      </c>
+      <c r="AC40">
+        <v>124080.7721792459</v>
+      </c>
+      <c r="AD40">
+        <v>39515.29723325667</v>
+      </c>
+      <c r="AE40">
+        <v>12423.51383371664</v>
+      </c>
+      <c r="AF40">
+        <v>44015.26238762282</v>
+      </c>
+      <c r="AG40">
+        <v>0.2746174970576697</v>
+      </c>
+      <c r="AH40">
+        <v>2.493961584173599</v>
+      </c>
+      <c r="AI40">
+        <v>4.246659815005138</v>
+      </c>
+      <c r="AJ40">
+        <v>30.00319332507171</v>
+      </c>
+      <c r="AK40">
+        <v>32.66959716735501</v>
+      </c>
+      <c r="AL40">
+        <v>17.45827984595635</v>
+      </c>
+      <c r="AM40">
+        <v>1.191910148250777</v>
+      </c>
+      <c r="AN40">
+        <v>0.8322628154711522</v>
+      </c>
+      <c r="AO40">
+        <v>1.206330118936819</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>South Carolina</t>
+        </is>
+      </c>
+      <c r="B41">
+        <v>41266.815</v>
+      </c>
+      <c r="C41">
+        <v>90552.099</v>
+      </c>
+      <c r="D41">
+        <v>2.194307920298671</v>
+      </c>
+      <c r="E41">
+        <v>0.307037311194741</v>
+      </c>
+      <c r="F41">
+        <v>1.096439159573739</v>
+      </c>
+      <c r="G41">
+        <v>1903048000</v>
+      </c>
+      <c r="H41">
+        <v>385182000</v>
+      </c>
+      <c r="I41">
+        <v>126634000</v>
+      </c>
+      <c r="J41">
+        <v>72919000</v>
+      </c>
+      <c r="K41">
+        <v>5.182</v>
+      </c>
+      <c r="L41">
+        <v>546.2910000000001</v>
+      </c>
+      <c r="M41">
+        <v>15.402</v>
+      </c>
+      <c r="N41">
+        <v>1545.711</v>
+      </c>
+      <c r="O41">
+        <v>3.453</v>
+      </c>
+      <c r="P41">
+        <v>304.299</v>
+      </c>
+      <c r="Q41">
+        <v>43.046</v>
+      </c>
+      <c r="R41">
+        <v>1024.109</v>
+      </c>
+      <c r="S41">
+        <v>351</v>
+      </c>
+      <c r="T41">
+        <v>172</v>
+      </c>
+      <c r="U41">
+        <v>541</v>
+      </c>
+      <c r="V41">
+        <v>12029.59601</v>
+      </c>
+      <c r="W41">
+        <v>16048.10832</v>
+      </c>
+      <c r="X41">
+        <v>25894.3477</v>
+      </c>
+      <c r="Y41">
+        <v>9395</v>
+      </c>
+      <c r="Z41">
+        <v>499</v>
+      </c>
+      <c r="AA41">
+        <v>1583775.861499206</v>
+      </c>
+      <c r="AB41">
+        <v>29346445.69419878</v>
+      </c>
+      <c r="AC41">
+        <v>21016.05618219849</v>
+      </c>
+      <c r="AD41">
+        <v>4253.705924586022</v>
+      </c>
+      <c r="AE41">
+        <v>1398.465650144675</v>
+      </c>
+      <c r="AF41">
+        <v>805.271228444964</v>
+      </c>
+      <c r="AG41">
+        <v>0.948578687915415</v>
+      </c>
+      <c r="AH41">
+        <v>1.134739187443929</v>
+      </c>
+      <c r="AI41">
+        <v>0.9964346504618262</v>
+      </c>
+      <c r="AJ41">
+        <v>4.203263519801116</v>
+      </c>
+      <c r="AK41">
+        <v>18.52941846608229</v>
+      </c>
+      <c r="AL41">
+        <v>5.311335816923895</v>
+      </c>
+      <c r="AM41">
+        <v>2.917803720991292</v>
+      </c>
+      <c r="AN41">
+        <v>1.071777411831428</v>
+      </c>
+      <c r="AO41">
+        <v>2.089259039338535</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>South Dakota</t>
+        </is>
+      </c>
+      <c r="B42">
+        <v>7750.985</v>
+      </c>
+      <c r="C42">
+        <v>17955.264</v>
+      </c>
+      <c r="D42">
+        <v>2.316513836628506</v>
+      </c>
+      <c r="E42">
+        <v>0.05528194962769693</v>
+      </c>
+      <c r="F42">
+        <v>0.197413448396652</v>
+      </c>
+      <c r="G42">
+        <v>245906000</v>
+      </c>
+      <c r="H42">
+        <v>98602000</v>
+      </c>
+      <c r="I42">
+        <v>113589000</v>
+      </c>
+      <c r="J42">
+        <v>37957000</v>
+      </c>
+      <c r="K42">
+        <v>2.585</v>
+      </c>
+      <c r="L42">
+        <v>591.032</v>
+      </c>
+      <c r="M42">
+        <v>17.775</v>
+      </c>
+      <c r="N42">
+        <v>2591.021</v>
+      </c>
+      <c r="O42">
+        <v>1</v>
+      </c>
+      <c r="P42">
+        <v>87.74899999999998</v>
+      </c>
+      <c r="Q42">
+        <v>9.333</v>
+      </c>
+      <c r="R42">
+        <v>135.644</v>
+      </c>
+      <c r="S42">
+        <v>51</v>
+      </c>
+      <c r="T42">
+        <v>15</v>
+      </c>
+      <c r="U42">
+        <v>75</v>
+      </c>
+      <c r="V42">
+        <v>4084.57771</v>
+      </c>
+      <c r="W42">
+        <v>1390.44752</v>
+      </c>
+      <c r="X42">
+        <v>4267.48265</v>
+      </c>
+      <c r="Y42">
+        <v>5886</v>
+      </c>
+      <c r="Z42">
+        <v>1018</v>
+      </c>
+      <c r="AA42">
+        <v>161510.5105799244</v>
+      </c>
+      <c r="AB42">
+        <v>1584063.063479546</v>
+      </c>
+      <c r="AC42">
+        <v>13695.48228307866</v>
+      </c>
+      <c r="AD42">
+        <v>5491.537189316738</v>
+      </c>
+      <c r="AE42">
+        <v>6326.222772330165</v>
+      </c>
+      <c r="AF42">
+        <v>2113.976157632659</v>
+      </c>
+      <c r="AG42">
+        <v>0.4373705653839386</v>
+      </c>
+      <c r="AH42">
+        <v>1.139614126656714</v>
+      </c>
+      <c r="AI42">
+        <v>0.6860230001995351</v>
+      </c>
+      <c r="AJ42">
+        <v>6.880510748724602</v>
+      </c>
+      <c r="AK42">
+        <v>9.807801720097119</v>
+      </c>
+      <c r="AL42">
+        <v>17.29527692830445</v>
+      </c>
+      <c r="AM42">
+        <v>1.248599087125704</v>
+      </c>
+      <c r="AN42">
+        <v>1.078789367037743</v>
+      </c>
+      <c r="AO42">
+        <v>1.757476389505649</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Tennessee</t>
+        </is>
+      </c>
+      <c r="B43">
+        <v>14065.821</v>
+      </c>
+      <c r="C43">
+        <v>37746.437</v>
+      </c>
+      <c r="D43">
+        <v>2.683557326657292</v>
+      </c>
+      <c r="E43">
+        <v>0.3618113942780878</v>
+      </c>
+      <c r="F43">
+        <v>1.292039001783911</v>
+      </c>
+      <c r="G43">
+        <v>1172329000</v>
+      </c>
+      <c r="H43">
+        <v>403701000</v>
+      </c>
+      <c r="I43">
+        <v>235296000</v>
+      </c>
+      <c r="J43">
+        <v>34839000</v>
+      </c>
+      <c r="K43">
+        <v>4.289000000000001</v>
+      </c>
+      <c r="L43">
+        <v>644.566</v>
+      </c>
+      <c r="M43">
+        <v>8.025</v>
+      </c>
+      <c r="N43">
+        <v>1704.905</v>
+      </c>
+      <c r="O43">
+        <v>9.231</v>
+      </c>
+      <c r="P43">
+        <v>556.434</v>
+      </c>
+      <c r="Q43">
+        <v>91.121</v>
+      </c>
+      <c r="R43">
+        <v>1833.03</v>
+      </c>
+      <c r="S43">
+        <v>155</v>
+      </c>
+      <c r="T43">
+        <v>418</v>
+      </c>
+      <c r="U43">
+        <v>643</v>
+      </c>
+      <c r="V43">
+        <v>13282.08868</v>
+      </c>
+      <c r="W43">
+        <v>28835.17347</v>
+      </c>
+      <c r="X43">
+        <v>34275.21279000001</v>
+      </c>
+      <c r="Y43">
+        <v>20331</v>
+      </c>
+      <c r="Z43">
+        <v>841</v>
+      </c>
+      <c r="AA43">
+        <v>1913879.973865343</v>
+      </c>
+      <c r="AB43">
+        <v>42972394.22715602</v>
+      </c>
+      <c r="AC43">
+        <v>31058.00422964424</v>
+      </c>
+      <c r="AD43">
+        <v>10695.07567032088</v>
+      </c>
+      <c r="AE43">
+        <v>6233.594974805172</v>
+      </c>
+      <c r="AF43">
+        <v>922.9745313445081</v>
+      </c>
+      <c r="AG43">
+        <v>0.6654089728592573</v>
+      </c>
+      <c r="AH43">
+        <v>1.658956857417052</v>
+      </c>
+      <c r="AI43">
+        <v>0.4707007135294929</v>
+      </c>
+      <c r="AJ43">
+        <v>4.971058847918473</v>
+      </c>
+      <c r="AK43">
+        <v>22.45302464833643</v>
+      </c>
+      <c r="AL43">
+        <v>4.136540258718214</v>
+      </c>
+      <c r="AM43">
+        <v>1.166985131136769</v>
+      </c>
+      <c r="AN43">
+        <v>1.449618468343482</v>
+      </c>
+      <c r="AO43">
+        <v>1.875991270833478</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Texas</t>
+        </is>
+      </c>
+      <c r="B44">
+        <v>80719.895</v>
+      </c>
+      <c r="C44">
+        <v>198465.385</v>
+      </c>
+      <c r="D44">
+        <v>2.458692308754861</v>
+      </c>
+      <c r="E44">
+        <v>0.2674167991561853</v>
+      </c>
+      <c r="F44">
+        <v>0.9549531598677223</v>
+      </c>
+      <c r="G44">
+        <v>9622499000</v>
+      </c>
+      <c r="H44">
+        <v>2101734000</v>
+      </c>
+      <c r="I44">
+        <v>432230000</v>
+      </c>
+      <c r="J44">
+        <v>2712603000</v>
+      </c>
+      <c r="K44">
+        <v>24.745</v>
+      </c>
+      <c r="L44">
+        <v>1999.67</v>
+      </c>
+      <c r="M44">
+        <v>33.761</v>
+      </c>
+      <c r="N44">
+        <v>8375.674999999999</v>
+      </c>
+      <c r="O44">
+        <v>57.88</v>
+      </c>
+      <c r="P44">
+        <v>1457.295</v>
+      </c>
+      <c r="Q44">
+        <v>893.9149999999998</v>
+      </c>
+      <c r="R44">
+        <v>6164.882</v>
+      </c>
+      <c r="S44">
+        <v>630</v>
+      </c>
+      <c r="T44">
+        <v>1285</v>
+      </c>
+      <c r="U44">
+        <v>1950</v>
+      </c>
+      <c r="V44">
+        <v>41025.34398000001</v>
+      </c>
+      <c r="W44">
+        <v>116488.25886</v>
+      </c>
+      <c r="X44">
+        <v>103068.3526</v>
+      </c>
+      <c r="Y44">
+        <v>55175</v>
+      </c>
+      <c r="Z44">
+        <v>789</v>
+      </c>
+      <c r="AA44">
+        <v>10721453.05629075</v>
+      </c>
+      <c r="AB44">
+        <v>373685880.6551725</v>
+      </c>
+      <c r="AC44">
+        <v>48484.52036106951</v>
+      </c>
+      <c r="AD44">
+        <v>10589.92730646707</v>
+      </c>
+      <c r="AE44">
+        <v>2177.860889948139</v>
+      </c>
+      <c r="AF44">
+        <v>13667.88974309046</v>
+      </c>
+      <c r="AG44">
+        <v>1.23745417993969</v>
+      </c>
+      <c r="AH44">
+        <v>3.971742166136574</v>
+      </c>
+      <c r="AI44">
+        <v>0.4030839305488812</v>
+      </c>
+      <c r="AJ44">
+        <v>14.50011533067462</v>
+      </c>
+      <c r="AK44">
+        <v>34.85403318871171</v>
+      </c>
+      <c r="AL44">
+        <v>1.429995468962392</v>
+      </c>
+      <c r="AM44">
+        <v>1.535636118754122</v>
+      </c>
+      <c r="AN44">
+        <v>1.103115466378772</v>
+      </c>
+      <c r="AO44">
+        <v>1.891948353504585</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Utah</t>
+        </is>
+      </c>
+      <c r="B45">
+        <v>5874.994000000001</v>
+      </c>
+      <c r="C45">
+        <v>16022.842</v>
+      </c>
+      <c r="D45">
+        <v>2.727295040641744</v>
+      </c>
+      <c r="E45">
+        <v>0.3063826629508049</v>
+      </c>
+      <c r="F45">
+        <v>1.094101391673138</v>
+      </c>
+      <c r="G45">
+        <v>938924000</v>
+      </c>
+      <c r="H45">
+        <v>258207000</v>
+      </c>
+      <c r="I45">
+        <v>67478000</v>
+      </c>
+      <c r="J45">
+        <v>412938000</v>
+      </c>
+      <c r="K45">
+        <v>2.078</v>
+      </c>
+      <c r="L45">
+        <v>684.641</v>
+      </c>
+      <c r="M45">
+        <v>5.09</v>
+      </c>
+      <c r="N45">
+        <v>1191.271</v>
+      </c>
+      <c r="O45">
+        <v>6.822</v>
+      </c>
+      <c r="P45">
+        <v>253.418</v>
+      </c>
+      <c r="Q45">
+        <v>20.662</v>
+      </c>
+      <c r="R45">
+        <v>656.245</v>
+      </c>
+      <c r="S45">
+        <v>53</v>
+      </c>
+      <c r="T45">
+        <v>102</v>
+      </c>
+      <c r="U45">
+        <v>121</v>
+      </c>
+      <c r="V45">
+        <v>5412.94914</v>
+      </c>
+      <c r="W45">
+        <v>13063.4082</v>
+      </c>
+      <c r="X45">
+        <v>11774.82612</v>
+      </c>
+      <c r="Y45">
+        <v>3056</v>
+      </c>
+      <c r="Z45">
+        <v>63</v>
+      </c>
+      <c r="AA45">
+        <v>1263000</v>
+      </c>
+      <c r="AB45">
+        <v>21427000</v>
+      </c>
+      <c r="AC45">
+        <v>58599.09247061164</v>
+      </c>
+      <c r="AD45">
+        <v>16114.93142103005</v>
+      </c>
+      <c r="AE45">
+        <v>4211.362753249392</v>
+      </c>
+      <c r="AF45">
+        <v>25771.83248764482</v>
+      </c>
+      <c r="AG45">
+        <v>0.3035167335873838</v>
+      </c>
+      <c r="AH45">
+        <v>2.69199504376169</v>
+      </c>
+      <c r="AI45">
+        <v>0.4272747342963943</v>
+      </c>
+      <c r="AJ45">
+        <v>3.148519226813157</v>
+      </c>
+      <c r="AK45">
+        <v>16.96516231195566</v>
+      </c>
+      <c r="AL45">
+        <v>2.06151832460733</v>
+      </c>
+      <c r="AM45">
+        <v>0.9791335301554303</v>
+      </c>
+      <c r="AN45">
+        <v>0.780806956640917</v>
+      </c>
+      <c r="AO45">
+        <v>1.027616023938365</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Vermont</t>
+        </is>
+      </c>
+      <c r="B46">
+        <v>2628.169</v>
+      </c>
+      <c r="C46">
+        <v>5997.863</v>
+      </c>
+      <c r="D46">
+        <v>2.282145097975054</v>
+      </c>
+      <c r="E46">
+        <v>0.1165935267277695</v>
+      </c>
+      <c r="F46">
+        <v>0.4163588716944298</v>
+      </c>
+      <c r="G46">
+        <v>194913000</v>
+      </c>
+      <c r="H46">
+        <v>117302000</v>
+      </c>
+      <c r="I46">
+        <v>81241000</v>
+      </c>
+      <c r="J46">
+        <v>79684000</v>
+      </c>
+      <c r="K46">
+        <v>2.919</v>
+      </c>
+      <c r="L46">
+        <v>255.284</v>
+      </c>
+      <c r="M46">
+        <v>5.902</v>
+      </c>
+      <c r="N46">
+        <v>328.649</v>
+      </c>
+      <c r="O46">
+        <v>0.881</v>
+      </c>
+      <c r="P46">
+        <v>64.30800000000001</v>
+      </c>
+      <c r="Q46">
+        <v>8.910999999999998</v>
+      </c>
+      <c r="R46">
+        <v>125.403</v>
+      </c>
+      <c r="S46">
+        <v>13</v>
+      </c>
+      <c r="T46">
+        <v>7</v>
+      </c>
+      <c r="U46">
+        <v>42</v>
+      </c>
+      <c r="V46">
+        <v>1577.74718</v>
+      </c>
+      <c r="W46">
+        <v>935.14707</v>
+      </c>
+      <c r="X46">
+        <v>3494.08084</v>
+      </c>
+      <c r="Y46">
+        <v>2836</v>
+      </c>
+      <c r="Z46">
+        <v>68</v>
+      </c>
+      <c r="AA46">
+        <v>65000</v>
+      </c>
+      <c r="AB46">
+        <v>1235000</v>
+      </c>
+      <c r="AC46">
+        <v>32497.07437465644</v>
+      </c>
+      <c r="AD46">
+        <v>19557.29899132407</v>
+      </c>
+      <c r="AE46">
+        <v>13544.99094094013</v>
+      </c>
+      <c r="AF46">
+        <v>13285.39848275961</v>
+      </c>
+      <c r="AG46">
+        <v>1.143432412528791</v>
+      </c>
+      <c r="AH46">
+        <v>1.36996952167693</v>
+      </c>
+      <c r="AI46">
+        <v>1.795836895898055</v>
+      </c>
+      <c r="AJ46">
+        <v>7.105890608677622</v>
+      </c>
+      <c r="AK46">
+        <v>19</v>
+      </c>
+      <c r="AL46">
+        <v>2.397743300423131</v>
+      </c>
+      <c r="AM46">
+        <v>0.8239596409863335</v>
+      </c>
+      <c r="AN46">
+        <v>0.748545359822386</v>
+      </c>
+      <c r="AO46">
+        <v>1.202032864242488</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Virginia</t>
+        </is>
+      </c>
+      <c r="B47">
+        <v>59247.388</v>
+      </c>
+      <c r="C47">
+        <v>128988.6</v>
+      </c>
+      <c r="D47">
+        <v>2.177118761758746</v>
+      </c>
+      <c r="E47">
+        <v>0.2473535413207059</v>
+      </c>
+      <c r="F47">
+        <v>0.8833066831778199</v>
+      </c>
+      <c r="G47">
+        <v>1530009000</v>
+      </c>
+      <c r="H47">
+        <v>1769492000</v>
+      </c>
+      <c r="I47">
+        <v>478453000</v>
+      </c>
+      <c r="J47">
+        <v>719842000</v>
+      </c>
+      <c r="K47">
+        <v>2.068</v>
+      </c>
+      <c r="L47">
+        <v>598.2</v>
+      </c>
+      <c r="M47">
+        <v>4.66</v>
+      </c>
+      <c r="N47">
+        <v>1635.352</v>
+      </c>
+      <c r="O47">
+        <v>13.358</v>
+      </c>
+      <c r="P47">
+        <v>520.7569999999999</v>
+      </c>
+      <c r="Q47">
+        <v>82.509</v>
+      </c>
+      <c r="R47">
+        <v>1353.132</v>
+      </c>
+      <c r="S47">
+        <v>175</v>
+      </c>
+      <c r="T47">
+        <v>216</v>
+      </c>
+      <c r="U47">
+        <v>458</v>
+      </c>
+      <c r="V47">
+        <v>14531.46916</v>
+      </c>
+      <c r="W47">
+        <v>31458.82974</v>
+      </c>
+      <c r="X47">
+        <v>30119.97032</v>
+      </c>
+      <c r="Y47">
+        <v>13997</v>
+      </c>
+      <c r="Z47">
+        <v>530</v>
+      </c>
+      <c r="AA47">
+        <v>1862692.487126011</v>
+      </c>
+      <c r="AB47">
+        <v>37093808.77450618</v>
+      </c>
+      <c r="AC47">
+        <v>11861.58311664752</v>
+      </c>
+      <c r="AD47">
+        <v>13718.20455451102</v>
+      </c>
+      <c r="AE47">
+        <v>3709.265780076689</v>
+      </c>
+      <c r="AF47">
+        <v>5580.663717568839</v>
+      </c>
+      <c r="AG47">
+        <v>0.3457037780006686</v>
+      </c>
+      <c r="AH47">
+        <v>2.565111942806338</v>
+      </c>
+      <c r="AI47">
+        <v>0.284953942637426</v>
+      </c>
+      <c r="AJ47">
+        <v>6.097631273223898</v>
+      </c>
+      <c r="AK47">
+        <v>19.91408084312351</v>
+      </c>
+      <c r="AL47">
+        <v>3.786525684075158</v>
+      </c>
+      <c r="AM47">
+        <v>1.204282912299832</v>
+      </c>
+      <c r="AN47">
+        <v>0.6866116819512689</v>
+      </c>
+      <c r="AO47">
+        <v>1.520585827722024</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Washington</t>
+        </is>
+      </c>
+      <c r="B48">
+        <v>7052.280000000001</v>
+      </c>
+      <c r="C48">
+        <v>18449.7</v>
+      </c>
+      <c r="D48">
+        <v>2.616132654971158</v>
+      </c>
+      <c r="E48">
+        <v>0.3229190718548269</v>
+      </c>
+      <c r="F48">
+        <v>1.15315338835244</v>
+      </c>
+      <c r="G48">
+        <v>1807166000</v>
+      </c>
+      <c r="H48">
+        <v>1048661000</v>
+      </c>
+      <c r="I48">
+        <v>299185000</v>
+      </c>
+      <c r="J48">
+        <v>586468000</v>
+      </c>
+      <c r="K48">
+        <v>17.6</v>
+      </c>
+      <c r="L48">
+        <v>428.99</v>
+      </c>
+      <c r="M48">
+        <v>15.64</v>
+      </c>
+      <c r="N48">
+        <v>1312.376</v>
+      </c>
+      <c r="O48">
+        <v>9.779999999999999</v>
+      </c>
+      <c r="P48">
+        <v>334.59</v>
+      </c>
+      <c r="Q48">
+        <v>246.557</v>
+      </c>
+      <c r="R48">
+        <v>1408.649</v>
+      </c>
+      <c r="S48">
+        <v>66</v>
+      </c>
+      <c r="T48">
+        <v>138</v>
+      </c>
+      <c r="U48">
+        <v>349</v>
+      </c>
+      <c r="V48">
+        <v>8151.52786</v>
+      </c>
+      <c r="W48">
+        <v>23958.66931</v>
+      </c>
+      <c r="X48">
+        <v>21548.04414</v>
+      </c>
+      <c r="Y48">
+        <v>8358</v>
+      </c>
+      <c r="Z48">
+        <v>401</v>
+      </c>
+      <c r="AA48">
+        <v>2764290.272976172</v>
+      </c>
+      <c r="AB48">
+        <v>67034058.31218909</v>
+      </c>
+      <c r="AC48">
+        <v>97950.96939245625</v>
+      </c>
+      <c r="AD48">
+        <v>56838.91879000742</v>
+      </c>
+      <c r="AE48">
+        <v>16216.25283879955</v>
+      </c>
+      <c r="AF48">
+        <v>31787.40033713285</v>
+      </c>
+      <c r="AG48">
+        <v>4.102659735658174</v>
+      </c>
+      <c r="AH48">
+        <v>2.922980364027616</v>
+      </c>
+      <c r="AI48">
+        <v>1.191731637884265</v>
+      </c>
+      <c r="AJ48">
+        <v>17.5030827409809</v>
+      </c>
+      <c r="AK48">
+        <v>24.25000694301793</v>
+      </c>
+      <c r="AL48">
+        <v>4.797798516391481</v>
+      </c>
+      <c r="AM48">
+        <v>0.809664165215771</v>
+      </c>
+      <c r="AN48">
+        <v>0.5759919226498977</v>
+      </c>
+      <c r="AO48">
+        <v>1.619636556025729</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>West Virginia</t>
+        </is>
+      </c>
+      <c r="B49">
+        <v>34421.598</v>
+      </c>
+      <c r="C49">
+        <v>71053.82399999999</v>
+      </c>
+      <c r="D49">
+        <v>2.064222120077051</v>
+      </c>
+      <c r="E49">
+        <v>0.126527518068556</v>
+      </c>
+      <c r="F49">
+        <v>0.4518334434151168</v>
+      </c>
+      <c r="G49">
+        <v>910892000</v>
+      </c>
+      <c r="H49">
+        <v>334687000</v>
+      </c>
+      <c r="I49">
+        <v>66194000</v>
+      </c>
+      <c r="J49">
+        <v>171927000</v>
+      </c>
+      <c r="K49">
+        <v>10.998</v>
+      </c>
+      <c r="L49">
+        <v>319.352</v>
+      </c>
+      <c r="M49">
+        <v>29.661</v>
+      </c>
+      <c r="N49">
+        <v>1012.214</v>
+      </c>
+      <c r="O49">
+        <v>21.142</v>
+      </c>
+      <c r="P49">
+        <v>235.238</v>
+      </c>
+      <c r="Q49">
+        <v>22.721</v>
+      </c>
+      <c r="R49">
+        <v>395.754</v>
+      </c>
+      <c r="S49">
+        <v>43</v>
+      </c>
+      <c r="T49">
+        <v>45</v>
+      </c>
+      <c r="U49">
+        <v>172</v>
+      </c>
+      <c r="V49">
+        <v>3780.86909</v>
+      </c>
+      <c r="W49">
+        <v>4739.48165</v>
+      </c>
+      <c r="X49">
+        <v>7533.78952</v>
+      </c>
+      <c r="Y49">
+        <v>7314</v>
+      </c>
+      <c r="Z49">
+        <v>1490</v>
+      </c>
+      <c r="AA49">
+        <v>378844.7775548986</v>
+      </c>
+      <c r="AB49">
+        <v>3779492.964293303</v>
+      </c>
+      <c r="AC49">
+        <v>12819.74633764961</v>
+      </c>
+      <c r="AD49">
+        <v>4710.3305798151</v>
+      </c>
+      <c r="AE49">
+        <v>931.6036248802036</v>
+      </c>
+      <c r="AF49">
+        <v>2419.672725847943</v>
+      </c>
+      <c r="AG49">
+        <v>3.443848793807461</v>
+      </c>
+      <c r="AH49">
+        <v>8.987493517203854</v>
+      </c>
+      <c r="AI49">
+        <v>2.930309203389797</v>
+      </c>
+      <c r="AJ49">
+        <v>5.74119276115971</v>
+      </c>
+      <c r="AK49">
+        <v>9.976362848886348</v>
+      </c>
+      <c r="AL49">
+        <v>20.37188952693464</v>
+      </c>
+      <c r="AM49">
+        <v>1.137304650767477</v>
+      </c>
+      <c r="AN49">
+        <v>0.949470919462258</v>
+      </c>
+      <c r="AO49">
+        <v>2.283047589043873</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Wisconsin</t>
+        </is>
+      </c>
+      <c r="B50">
+        <v>11747.23</v>
+      </c>
+      <c r="C50">
+        <v>29805.73</v>
+      </c>
+      <c r="D50">
+        <v>2.537256016950379</v>
+      </c>
+      <c r="E50">
+        <v>0.2592380726793136</v>
+      </c>
+      <c r="F50">
+        <v>0.9257466899771722</v>
+      </c>
+      <c r="G50">
+        <v>1384617000</v>
+      </c>
+      <c r="H50">
+        <v>349633000</v>
+      </c>
+      <c r="I50">
+        <v>180214000</v>
+      </c>
+      <c r="J50">
+        <v>624653000</v>
+      </c>
+      <c r="K50">
+        <v>13.34</v>
+      </c>
+      <c r="L50">
+        <v>508.16</v>
+      </c>
+      <c r="M50">
+        <v>43.12</v>
+      </c>
+      <c r="N50">
+        <v>2825.275</v>
+      </c>
+      <c r="O50">
+        <v>19.161</v>
+      </c>
+      <c r="P50">
+        <v>366.16</v>
+      </c>
+      <c r="Q50">
+        <v>327.233</v>
+      </c>
+      <c r="R50">
+        <v>1891.135</v>
+      </c>
+      <c r="S50">
+        <v>107</v>
+      </c>
+      <c r="T50">
+        <v>122</v>
+      </c>
+      <c r="U50">
+        <v>381</v>
+      </c>
+      <c r="V50">
+        <v>11964.82587</v>
+      </c>
+      <c r="W50">
+        <v>18202.47359</v>
+      </c>
+      <c r="X50">
+        <v>27432.64157</v>
+      </c>
+      <c r="Y50">
+        <v>14307</v>
+      </c>
+      <c r="Z50">
+        <v>987</v>
+      </c>
+      <c r="AA50">
+        <v>1865384.175558555</v>
+      </c>
+      <c r="AB50">
+        <v>31764951.59595602</v>
+      </c>
+      <c r="AC50">
+        <v>46454.72531623953</v>
+      </c>
+      <c r="AD50">
+        <v>11730.39546422785</v>
+      </c>
+      <c r="AE50">
+        <v>6046.287072988986</v>
+      </c>
+      <c r="AF50">
+        <v>20957.48032341432</v>
+      </c>
+      <c r="AG50">
+        <v>2.625157430730479</v>
+      </c>
+      <c r="AH50">
+        <v>5.232958269608915</v>
+      </c>
+      <c r="AI50">
+        <v>1.52622311102459</v>
+      </c>
+      <c r="AJ50">
+        <v>17.3035240741671</v>
+      </c>
+      <c r="AK50">
+        <v>17.02863786031882</v>
+      </c>
+      <c r="AL50">
+        <v>6.898720905850284</v>
+      </c>
+      <c r="AM50">
+        <v>0.8942879834823706</v>
+      </c>
+      <c r="AN50">
+        <v>0.6702385771735103</v>
+      </c>
+      <c r="AO50">
+        <v>1.388856406802096</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Wyoming</t>
+        </is>
+      </c>
+      <c r="B51">
+        <v>6734.893</v>
+      </c>
+      <c r="C51">
+        <v>15792.422</v>
+      </c>
+      <c r="D51">
+        <v>2.344866058005673</v>
+      </c>
+      <c r="E51">
+        <v>0.09470820878520091</v>
+      </c>
+      <c r="F51">
+        <v>0.3382057654202076</v>
+      </c>
+      <c r="G51">
+        <v>374234000</v>
+      </c>
+      <c r="H51">
+        <v>106393000</v>
+      </c>
+      <c r="I51">
+        <v>42152000</v>
+      </c>
+      <c r="J51">
+        <v>41598000</v>
+      </c>
+      <c r="K51">
+        <v>12.717</v>
+      </c>
+      <c r="L51">
+        <v>807.0499999999998</v>
+      </c>
+      <c r="M51">
+        <v>5.921</v>
+      </c>
+      <c r="N51">
+        <v>1914.304</v>
+      </c>
+      <c r="O51">
+        <v>7.081</v>
+      </c>
+      <c r="P51">
+        <v>105.653</v>
+      </c>
+      <c r="Q51">
+        <v>11.374</v>
+      </c>
+      <c r="R51">
+        <v>191.407</v>
+      </c>
+      <c r="S51">
+        <v>56</v>
+      </c>
+      <c r="T51">
+        <v>17</v>
+      </c>
+      <c r="U51">
+        <v>53</v>
+      </c>
+      <c r="V51">
+        <v>4147.37377</v>
+      </c>
+      <c r="W51">
+        <v>1239.22442</v>
+      </c>
+      <c r="X51">
+        <v>4413.721619999999</v>
+      </c>
+      <c r="Y51">
+        <v>3114</v>
+      </c>
+      <c r="Z51">
+        <v>230</v>
+      </c>
+      <c r="AA51">
+        <v>89000</v>
+      </c>
+      <c r="AB51">
+        <v>578000</v>
+      </c>
+      <c r="AC51">
+        <v>23697.06179330821</v>
+      </c>
+      <c r="AD51">
+        <v>6736.965362247792</v>
+      </c>
+      <c r="AE51">
+        <v>2669.128269242045</v>
+      </c>
+      <c r="AF51">
+        <v>2634.048152968557</v>
+      </c>
+      <c r="AG51">
+        <v>1.575738801809058</v>
+      </c>
+      <c r="AH51">
+        <v>6.702128666483678</v>
+      </c>
+      <c r="AI51">
+        <v>0.3093030156129852</v>
+      </c>
+      <c r="AJ51">
+        <v>5.942311409718558</v>
+      </c>
+      <c r="AK51">
+        <v>6.49438202247191</v>
+      </c>
+      <c r="AL51">
+        <v>7.385998715478484</v>
+      </c>
+      <c r="AM51">
+        <v>1.350252065658408</v>
+      </c>
+      <c r="AN51">
+        <v>1.371825774705117</v>
+      </c>
+      <c r="AO51">
+        <v>1.200800697530172</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B52">
+        <v>781295.8360000001</v>
+      </c>
+      <c r="C52">
+        <v>1887581.177</v>
+      </c>
+      <c r="D52">
+        <v>2.415962161866686</v>
+      </c>
+      <c r="E52">
+        <v>15.2681954868892</v>
+      </c>
+      <c r="F52">
+        <v>54.52316971742386</v>
+      </c>
+      <c r="G52">
+        <v>78869455000</v>
+      </c>
+      <c r="H52">
+        <v>27457186000</v>
+      </c>
+      <c r="I52">
+        <v>10083635000</v>
+      </c>
+      <c r="J52">
+        <v>41353230000</v>
+      </c>
+      <c r="K52">
+        <v>609.4630000000001</v>
+      </c>
+      <c r="L52">
+        <v>29198.70900000001</v>
+      </c>
+      <c r="M52">
+        <v>1016.447</v>
+      </c>
+      <c r="N52">
+        <v>89777.72099999999</v>
+      </c>
+      <c r="O52">
+        <v>910.6830000000001</v>
+      </c>
+      <c r="P52">
+        <v>19108.484</v>
+      </c>
+      <c r="Q52">
+        <v>9104.541999999996</v>
+      </c>
+      <c r="R52">
+        <v>64182.55</v>
+      </c>
+      <c r="S52">
+        <v>5822</v>
+      </c>
+      <c r="T52">
+        <v>11889</v>
+      </c>
+      <c r="U52">
+        <v>20174</v>
+      </c>
+      <c r="V52">
+        <v>448887.9185199999</v>
+      </c>
+      <c r="W52">
+        <v>1143597.16534</v>
+      </c>
+      <c r="X52">
+        <v>1308105.96845</v>
+      </c>
+      <c r="Y52">
+        <v>617008</v>
+      </c>
+      <c r="Z52">
+        <v>43289</v>
+      </c>
+      <c r="AA52">
+        <v>112772000</v>
+      </c>
+      <c r="AB52">
+        <v>3049151000</v>
+      </c>
+      <c r="AC52">
+        <v>41783.34471704684</v>
+      </c>
+      <c r="AD52">
+        <v>14546.22791038777</v>
+      </c>
+      <c r="AE52">
+        <v>5342.093427751955</v>
+      </c>
+      <c r="AF52">
+        <v>21908.05381187587</v>
+      </c>
+      <c r="AG52">
+        <v>2.087294338938067</v>
+      </c>
+      <c r="AH52">
+        <v>4.765856883256673</v>
+      </c>
+      <c r="AI52">
+        <v>1.132181780377339</v>
+      </c>
+      <c r="AJ52">
+        <v>14.18538527995537</v>
+      </c>
+      <c r="AK52">
+        <v>27.03819210442308</v>
+      </c>
+      <c r="AL52">
+        <v>7.015954412260457</v>
+      </c>
+      <c r="AM52">
+        <v>1.296983001724651</v>
+      </c>
+      <c r="AN52">
+        <v>1.039614329269985</v>
+      </c>
+      <c r="AO52">
+        <v>1.542229795335661</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>